--- a/outputs/validation_truss_temperature.xlsx
+++ b/outputs/validation_truss_temperature.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="G4" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>155.8845726811995</v>
+        <v>155.8845726811993</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="F5" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="G5" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="F6" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="F7" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="G7" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>201.2461179749813</v>
+        <v>201.2461179749812</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="F8" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="G8" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>311.7691453623987</v>
+        <v>311.7691453623984</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="F9" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="G9" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>324.4996147917596</v>
+        <v>324.4996147917595</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="F10" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="F11" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="G11" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>371.0795063055898</v>
+        <v>371.0795063055897</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="F12" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="G12" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>412.4318125460265</v>
+        <v>412.4318125460267</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="F13" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="G13" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>422.1374183841098</v>
+        <v>422.1374183841095</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="F14" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="F15" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>547.4486277268403</v>
+        <v>547.4486277268401</v>
       </c>
     </row>
   </sheetData>
@@ -1035,13 +1035,13 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>547.4486277268403</v>
+        <v>547.4486277268401</v>
       </c>
       <c r="D2" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="E2" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1057,13 +1057,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="D3" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="E3" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="D4" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="E4" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1101,16 +1101,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="D5" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="E5" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="F5" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.421438694000244e-08</v>
+        <v>-1.676380634307861e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.313225746154785e-08</v>
+        <v>-6.705522537231445e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.142041921615601e-08</v>
+        <v>-1.490116119384766e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.080334186553955e-07</v>
+        <v>6.705522537231445e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.955777406692505e-08</v>
+        <v>4.656612873077393e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7.450580596923828e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-8.381903171539307e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="G2" t="n">
-        <v>30.00000000000016</v>
+        <v>30.00000000000013</v>
       </c>
       <c r="H2" t="n">
-        <v>8400000.000000043</v>
+        <v>8400000.000000037</v>
       </c>
       <c r="I2" t="n">
-        <v>2100000000.000011</v>
+        <v>2100000000.000009</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>155.8845726811995</v>
+        <v>155.8845726811993</v>
       </c>
       <c r="G3" t="n">
-        <v>30.00000000000011</v>
+        <v>30.00000000000006</v>
       </c>
       <c r="H3" t="n">
-        <v>8400000.000000032</v>
+        <v>8400000.000000019</v>
       </c>
       <c r="I3" t="n">
-        <v>2100000000.000008</v>
+        <v>2100000000.000005</v>
       </c>
     </row>
     <row r="4">
@@ -1337,13 +1337,13 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>89.99999999999999</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>8399999.999999998</v>
+        <v>8400000</v>
       </c>
       <c r="I4" t="n">
         <v>2100000000</v>
@@ -1368,13 +1368,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>155.8845726811991</v>
+        <v>155.884572681199</v>
       </c>
       <c r="G5" t="n">
-        <v>30.00000000000002</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>8400000.000000006</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="I5" t="n">
         <v>2100000000.000001</v>
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>179.9999999999999</v>
+        <v>180</v>
       </c>
       <c r="G6" t="n">
-        <v>29.99999999999999</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>8399999.999999996</v>
+        <v>8400000</v>
       </c>
       <c r="I6" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000</v>
       </c>
     </row>
     <row r="7">
@@ -1433,13 +1433,13 @@
         <v>180.0000000000004</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00000000000006</v>
+        <v>30.00000000000007</v>
       </c>
       <c r="H7" t="n">
-        <v>8400000.000000017</v>
+        <v>8400000.000000019</v>
       </c>
       <c r="I7" t="n">
-        <v>2100000000.000004</v>
+        <v>2100000000.000005</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>180</v>
+        <v>179.9999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H8" t="n">
-        <v>8400000</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="I8" t="n">
-        <v>2100000000</v>
+        <v>2099999999.999998</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>155.8845726811988</v>
+        <v>155.884572681199</v>
       </c>
       <c r="G9" t="n">
-        <v>29.99999999999997</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>8399999.999999991</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="I9" t="n">
-        <v>2099999999.999998</v>
+        <v>2100000000.000001</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>89.99999999999994</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="G10" t="n">
-        <v>29.99999999999998</v>
+        <v>30.00000000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>8399999.999999994</v>
+        <v>8400000.000000006</v>
       </c>
       <c r="I10" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000.000001</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>180.0000000000002</v>
+        <v>180.0000000000004</v>
       </c>
       <c r="G11" t="n">
-        <v>30.00000000000003</v>
+        <v>30.00000000000007</v>
       </c>
       <c r="H11" t="n">
-        <v>8400000.000000007</v>
+        <v>8400000.000000019</v>
       </c>
       <c r="I11" t="n">
-        <v>2100000000.000002</v>
+        <v>2100000000.000005</v>
       </c>
     </row>
     <row r="12">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="G13" t="n">
-        <v>29.99999999999979</v>
+        <v>29.99999999999982</v>
       </c>
       <c r="H13" t="n">
-        <v>8399999.99999994</v>
+        <v>8399999.99999995</v>
       </c>
       <c r="I13" t="n">
-        <v>2099999999.999985</v>
+        <v>2099999999.999987</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>155.8845726811984</v>
+        <v>155.8845726811988</v>
       </c>
       <c r="G14" t="n">
-        <v>29.99999999999989</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>8399999.99999997</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="I14" t="n">
-        <v>2099999999.999993</v>
+        <v>2099999999.999999</v>
       </c>
     </row>
     <row r="15">
@@ -1678,7 +1678,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>89.99999999999996</v>
+        <v>89.99999999999997</v>
       </c>
       <c r="G15" t="n">
         <v>29.99999999999999</v>
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>155.8845726811988</v>
+        <v>155.884572681199</v>
       </c>
       <c r="G16" t="n">
-        <v>29.99999999999998</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>8399999.999999994</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="I16" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000.000001</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>179.9999999999999</v>
+        <v>179.9999999999997</v>
       </c>
       <c r="G17" t="n">
-        <v>29.99999999999998</v>
+        <v>29.99999999999995</v>
       </c>
       <c r="H17" t="n">
-        <v>8399999.999999994</v>
+        <v>8399999.999999987</v>
       </c>
       <c r="I17" t="n">
-        <v>2099999999.999999</v>
+        <v>2099999999.999997</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>179.9999999999994</v>
+        <v>179.9999999999995</v>
       </c>
       <c r="G18" t="n">
-        <v>29.9999999999999</v>
+        <v>29.99999999999991</v>
       </c>
       <c r="H18" t="n">
-        <v>8399999.99999997</v>
+        <v>8399999.999999976</v>
       </c>
       <c r="I18" t="n">
-        <v>2099999999.999993</v>
+        <v>2099999999.999994</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>179.9999999999999</v>
+        <v>180</v>
       </c>
       <c r="G19" t="n">
-        <v>29.99999999999998</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
-        <v>8399999.999999994</v>
+        <v>8400000</v>
       </c>
       <c r="I19" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>155.8845726811992</v>
+        <v>155.8845726811991</v>
       </c>
       <c r="G20" t="n">
-        <v>30.00000000000004</v>
+        <v>30.00000000000003</v>
       </c>
       <c r="H20" t="n">
-        <v>8400000.000000011</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="I20" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>89.99999999999994</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H21" t="n">
-        <v>8400000</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="I21" t="n">
-        <v>2100000000</v>
+        <v>2099999999.999999</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>179.9999999999997</v>
+        <v>179.9999999999995</v>
       </c>
       <c r="G22" t="n">
-        <v>29.99999999999995</v>
+        <v>29.99999999999993</v>
       </c>
       <c r="H22" t="n">
-        <v>8399999.999999987</v>
+        <v>8399999.999999978</v>
       </c>
       <c r="I22" t="n">
-        <v>2099999999.999997</v>
+        <v>2099999999.999994</v>
       </c>
     </row>
     <row r="23">
@@ -1929,13 +1929,13 @@
         <v>155.8845726811991</v>
       </c>
       <c r="G23" t="n">
-        <v>30.00000000000002</v>
+        <v>30.00000000000003</v>
       </c>
       <c r="H23" t="n">
-        <v>8400000.000000006</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="I23" t="n">
-        <v>2100000000.000001</v>
+        <v>2100000000.000002</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="G24" t="n">
-        <v>30.00000000000004</v>
+        <v>30.00000000000002</v>
       </c>
       <c r="H24" t="n">
-        <v>8400000.000000009</v>
+        <v>8400000.000000006</v>
       </c>
       <c r="I24" t="n">
-        <v>2100000000.000002</v>
+        <v>2100000000.000001</v>
       </c>
     </row>
     <row r="25">
@@ -1988,13 +1988,13 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>89.99999999999993</v>
+        <v>89.99999999999991</v>
       </c>
       <c r="G25" t="n">
-        <v>29.99999999999998</v>
+        <v>29.99999999999997</v>
       </c>
       <c r="H25" t="n">
-        <v>8399999.999999993</v>
+        <v>8399999.999999991</v>
       </c>
       <c r="I25" t="n">
         <v>2099999999.999998</v>
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>89.99999999999994</v>
+        <v>89.99999999999993</v>
       </c>
       <c r="G27" t="n">
         <v>29.99999999999998</v>
       </c>
       <c r="H27" t="n">
-        <v>8399999.999999994</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="I27" t="n">
-        <v>2099999999.999999</v>
+        <v>2099999999.999998</v>
       </c>
     </row>
     <row r="28">
@@ -2112,16 +2112,16 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>90</v>
+        <v>89.99999999999989</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>29.99999999999996</v>
       </c>
       <c r="H29" t="n">
-        <v>8400000</v>
+        <v>8399999.999999989</v>
       </c>
       <c r="I29" t="n">
-        <v>2100000000</v>
+        <v>2099999999.999997</v>
       </c>
     </row>
     <row r="30">
@@ -2143,16 +2143,16 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>89.99999999999997</v>
+        <v>89.99999999999993</v>
       </c>
       <c r="G30" t="n">
-        <v>29.99999999999999</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H30" t="n">
-        <v>8399999.999999996</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="I30" t="n">
-        <v>2099999999.999999</v>
+        <v>2099999999.999998</v>
       </c>
     </row>
     <row r="31">
@@ -2180,10 +2180,10 @@
         <v>30.00000000000005</v>
       </c>
       <c r="H31" t="n">
-        <v>8400000.000000015</v>
+        <v>8400000.000000013</v>
       </c>
       <c r="I31" t="n">
-        <v>2100000000.000004</v>
+        <v>2100000000.000003</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>179.9999999999997</v>
+        <v>179.9999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>29.99999999999995</v>
+        <v>29.99999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>8399999.999999987</v>
+        <v>8399999.999999996</v>
       </c>
       <c r="I32" t="n">
-        <v>2099999999.999997</v>
+        <v>2099999999.999999</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>201.2461179749813</v>
+        <v>201.2461179749812</v>
       </c>
       <c r="G33" t="n">
-        <v>30.00000000000003</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>8400000.000000009</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="I33" t="n">
-        <v>2100000000.000002</v>
+        <v>2100000000.000001</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>201.2461179749806</v>
+        <v>201.2461179749808</v>
       </c>
       <c r="G34" t="n">
-        <v>29.99999999999993</v>
+        <v>29.99999999999995</v>
       </c>
       <c r="H34" t="n">
-        <v>8399999.999999981</v>
+        <v>8399999.999999987</v>
       </c>
       <c r="I34" t="n">
-        <v>2099999999.999995</v>
+        <v>2099999999.999997</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>180.0000000000003</v>
+        <v>180.0000000000002</v>
       </c>
       <c r="G35" t="n">
-        <v>30.00000000000005</v>
+        <v>30.00000000000003</v>
       </c>
       <c r="H35" t="n">
-        <v>8400000.000000013</v>
+        <v>8400000.000000007</v>
       </c>
       <c r="I35" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>179.9999999999997</v>
+        <v>179.9999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>29.99999999999994</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H36" t="n">
-        <v>8399999.999999983</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="I36" t="n">
-        <v>2099999999.999996</v>
+        <v>2099999999.999999</v>
       </c>
     </row>
     <row r="37">
@@ -2363,10 +2363,10 @@
         <v>201.2461179749812</v>
       </c>
       <c r="G37" t="n">
-        <v>30.00000000000002</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>8400000.000000006</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="I37" t="n">
         <v>2100000000.000001</v>
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>201.2461179749807</v>
+        <v>201.2461179749809</v>
       </c>
       <c r="G38" t="n">
-        <v>29.99999999999994</v>
+        <v>29.99999999999997</v>
       </c>
       <c r="H38" t="n">
-        <v>8399999.999999985</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="I38" t="n">
-        <v>2099999999.999996</v>
+        <v>2099999999.999998</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>180.0000000000003</v>
+        <v>180.0000000000002</v>
       </c>
       <c r="G39" t="n">
-        <v>30.00000000000005</v>
+        <v>30.00000000000004</v>
       </c>
       <c r="H39" t="n">
-        <v>8400000.000000013</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="I39" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>179.9999999999998</v>
+        <v>179.9999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>29.99999999999996</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H40" t="n">
-        <v>8399999.999999989</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="I40" t="n">
-        <v>2099999999.999997</v>
+        <v>2099999999.999999</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>201.2461179749814</v>
+        <v>201.2461179749813</v>
       </c>
       <c r="G41" t="n">
-        <v>30.00000000000004</v>
+        <v>30.00000000000003</v>
       </c>
       <c r="H41" t="n">
-        <v>8400000.000000013</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="I41" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>201.2461179749807</v>
+        <v>201.2461179749808</v>
       </c>
       <c r="G42" t="n">
-        <v>29.99999999999994</v>
+        <v>29.99999999999996</v>
       </c>
       <c r="H42" t="n">
-        <v>8399999.999999983</v>
+        <v>8399999.999999989</v>
       </c>
       <c r="I42" t="n">
-        <v>2099999999.999996</v>
+        <v>2099999999.999997</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>179.9999999999999</v>
+        <v>180.0000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>29.99999999999999</v>
+        <v>30.00000000000002</v>
       </c>
       <c r="H43" t="n">
-        <v>8399999.999999996</v>
+        <v>8400000.000000006</v>
       </c>
       <c r="I43" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000.000001</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>180.0000000000001</v>
+        <v>179.9999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>30.00000000000002</v>
+        <v>29.99999999999998</v>
       </c>
       <c r="H44" t="n">
-        <v>8400000.000000006</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="I44" t="n">
-        <v>2100000000.000001</v>
+        <v>2099999999.999999</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>8400000.000000043</v>
+        <v>8400000.000000037</v>
       </c>
       <c r="F2" t="n">
-        <v>2100000000.000011</v>
+        <v>2100000000.000009</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="N2" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2.968575733106793e-12</v>
+        <v>-2.329516727335206e-12</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4.656612873077393e-08</v>
+        <v>-3.91155481338501e-08</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>4.656612873077393e-08</v>
+        <v>3.91155481338501e-08</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>8400000.000000032</v>
+        <v>8400000.000000019</v>
       </c>
       <c r="F3" t="n">
-        <v>2100000000.000008</v>
+        <v>2100000000.000005</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="N3" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="O3" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>155.8845726811995</v>
+        <v>155.8845726811993</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>1.179500941361766e-12</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.627271987320841e-12</v>
+        <v>-8.093987077986736e-13</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3.166496753692627e-08</v>
+        <v>-1.862645149230957e-08</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.166496753692627e-08</v>
+        <v>1.862645149230957e-08</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>8399999.999999998</v>
+        <v>8400000</v>
       </c>
       <c r="F4" t="n">
         <v>2100000000</v>
       </c>
       <c r="G4" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="H4" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="I4" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="N4" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.008970684779342e-12</v>
+        <v>1.165290086646564e-12</v>
       </c>
       <c r="T4" t="n">
-        <v>155.8845726811995</v>
+        <v>155.8845726811993</v>
       </c>
       <c r="U4" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>90.00000000000099</v>
+        <v>90.00000000000117</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.8845726811995</v>
+        <v>155.8845726811992</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>8400000.000000006</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="F5" t="n">
         <v>2100000000.000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="H5" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="I5" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="N5" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="O5" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>155.8845726811995</v>
+        <v>155.8845726811993</v>
       </c>
       <c r="T5" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>1.179500941361766e-12</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.627271987320841e-12</v>
+        <v>-8.093987077986736e-13</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>311.7691453623986</v>
+        <v>311.7691453623983</v>
       </c>
       <c r="Z5" t="n">
         <v>1.392663762089796e-12</v>
       </c>
       <c r="AA5" t="n">
-        <v>-4.352044038901301e-12</v>
+        <v>-1.862315955609786e-12</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-5.587935447692871e-09</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.587935447692871e-09</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>8399999.999999996</v>
+        <v>8400000</v>
       </c>
       <c r="F6" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000</v>
       </c>
       <c r="G6" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="N6" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="O6" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>89.99999999999994</v>
+        <v>89.99999999999963</v>
       </c>
       <c r="T6" t="n">
         <v>155.8845726812001</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.968575733106793e-12</v>
+        <v>-2.329516727335206e-12</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>269.9999999999999</v>
+        <v>269.9999999999997</v>
       </c>
       <c r="Z6" t="n">
-        <v>155.8845726812005</v>
+        <v>155.8845726812004</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.352044038901301e-12</v>
+        <v>-1.862315955609786e-12</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>8400000.000000017</v>
+        <v>8400000.000000019</v>
       </c>
       <c r="F7" t="n">
-        <v>2100000000.000004</v>
+        <v>2100000000.000005</v>
       </c>
       <c r="G7" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="H7" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="N7" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.968575733106793e-12</v>
+        <v>-2.329516727335206e-12</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8.931538245898027e-12</v>
+        <v>-7.292197765110538e-12</v>
       </c>
       <c r="AA7" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>8400000</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="F8" t="n">
-        <v>2100000000</v>
+        <v>2099999999.999998</v>
       </c>
       <c r="G8" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="H8" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="I8" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="N8" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3642,10 +3642,10 @@
         <v>1.392663762089796e-12</v>
       </c>
       <c r="T8" t="n">
-        <v>311.7691453623986</v>
+        <v>311.7691453623984</v>
       </c>
       <c r="U8" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>180.0000000000014</v>
+        <v>180.0000000000013</v>
       </c>
       <c r="Z8" t="n">
-        <v>311.7691453623986</v>
+        <v>311.7691453623985</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,25 +3675,25 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
+        <v>3.725290298461914e-09</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
         <v>-3.725290298461914e-09</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>3.725290298461914e-09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>8399999.999999991</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="F9" t="n">
-        <v>2099999999.999998</v>
+        <v>2100000000.000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="H9" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="I9" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="N9" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="O9" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>155.8845726812005</v>
+        <v>155.8845726812004</v>
       </c>
       <c r="T9" t="n">
-        <v>269.9999999999999</v>
+        <v>269.9999999999997</v>
       </c>
       <c r="U9" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>311.7691453623993</v>
+        <v>311.7691453623994</v>
       </c>
       <c r="Z9" t="n">
-        <v>269.9999999999998</v>
+        <v>270</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-1.862645149230957e-09</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>1.862645149230957e-09</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>8399999.999999994</v>
+        <v>8400000.000000006</v>
       </c>
       <c r="F10" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000.000001</v>
       </c>
       <c r="G10" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="H10" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="I10" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="N10" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="O10" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3898,28 +3898,28 @@
         <v>179.9999999999999</v>
       </c>
       <c r="T10" t="n">
+        <v>311.7691453623993</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-7.292197765110538e-12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>270</v>
+      </c>
+      <c r="Z10" t="n">
         <v>311.7691453623995</v>
       </c>
-      <c r="U10" t="n">
-        <v>-8.931538245898027e-12</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>269.9999999999998</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>311.7691453623994</v>
-      </c>
       <c r="AA10" t="n">
-        <v>-1.105109697137119e-11</v>
+        <v>-8.25034530002525e-12</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>8400000.000000007</v>
+        <v>8400000.000000019</v>
       </c>
       <c r="F11" t="n">
-        <v>2100000000.000002</v>
+        <v>2100000000.000005</v>
       </c>
       <c r="G11" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="H11" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="N11" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.931538245898027e-12</v>
+        <v>-7.292197765110538e-12</v>
       </c>
       <c r="U11" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.651056362690877e-11</v>
+        <v>-1.421950808161317e-11</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4115,13 +4115,13 @@
         <v>2099999999.999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="H12" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="I12" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="N12" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>311.7691453623993</v>
+        <v>311.7691453623994</v>
       </c>
       <c r="T12" t="n">
-        <v>269.9999999999998</v>
+        <v>270</v>
       </c>
       <c r="U12" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>467.6537180435981</v>
+        <v>467.6537180435982</v>
       </c>
       <c r="Z12" t="n">
-        <v>270.0000000000007</v>
+        <v>270.0000000000008</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>8399999.99999994</v>
+        <v>8399999.99999995</v>
       </c>
       <c r="F13" t="n">
-        <v>2099999999.999985</v>
+        <v>2099999999.999987</v>
       </c>
       <c r="G13" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="N13" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="O13" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-90.00000000000011</v>
+        <v>-90.00000000000006</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="Z13" t="n">
-        <v>-90.000000000003</v>
+        <v>-90.00000000000236</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>5.587935447692871e-08</v>
+        <v>4.842877388000488e-08</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-5.587935447692871e-08</v>
+        <v>-4.842877388000488e-08</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>8399999.99999997</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="F14" t="n">
-        <v>2099999999.999993</v>
+        <v>2099999999.999999</v>
       </c>
       <c r="G14" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="N14" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="O14" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-90.00000000000011</v>
+        <v>-90.00000000000006</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>155.8845726811984</v>
+        <v>155.8845726811988</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.890043677121866e-12</v>
+        <v>-2.586375558166765e-12</v>
       </c>
       <c r="AA14" t="n">
-        <v>-90.00000000000156</v>
+        <v>-90.00000000000072</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>5.587935447692871e-09</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-5.587935447692871e-09</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4499,13 +4499,13 @@
         <v>2099999999.999999</v>
       </c>
       <c r="G15" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="H15" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="I15" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="N15" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="O15" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.904254531837068e-12</v>
+        <v>-2.600586412881967e-12</v>
       </c>
       <c r="T15" t="n">
-        <v>155.8845726811984</v>
+        <v>155.8845726811988</v>
       </c>
       <c r="U15" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>89.99999999999805</v>
+        <v>89.99999999999737</v>
       </c>
       <c r="Z15" t="n">
-        <v>155.8845726811986</v>
+        <v>155.8845726811992</v>
       </c>
       <c r="AA15" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>8399999.999999994</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="F16" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000.000001</v>
       </c>
       <c r="G16" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="H16" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="I16" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="N16" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="O16" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>155.8845726811984</v>
+        <v>155.8845726811988</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.890043677121866e-12</v>
+        <v>-2.586375558166765e-12</v>
       </c>
       <c r="U16" t="n">
-        <v>-90.00000000000156</v>
+        <v>-90.00000000000072</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>311.7691453623972</v>
+        <v>311.7691453623979</v>
       </c>
       <c r="Z16" t="n">
-        <v>-2.188471626141109e-12</v>
+        <v>-2.472688720445149e-12</v>
       </c>
       <c r="AA16" t="n">
-        <v>-90.00000000000429</v>
+        <v>-90.00000000000179</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-1.862645149230957e-09</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>1.862645149230957e-09</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>8399999.999999994</v>
+        <v>8399999.999999987</v>
       </c>
       <c r="F17" t="n">
-        <v>2099999999.999999</v>
+        <v>2099999999.999997</v>
       </c>
       <c r="G17" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="H17" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="I17" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="N17" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="O17" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>90.0000000000007</v>
+        <v>90.00000000000155</v>
       </c>
       <c r="T17" t="n">
-        <v>155.8845726811971</v>
+        <v>155.8845726811968</v>
       </c>
       <c r="U17" t="n">
-        <v>-90.000000000003</v>
+        <v>-90.00000000000236</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>270.0000000000006</v>
+        <v>270.0000000000013</v>
       </c>
       <c r="Z17" t="n">
-        <v>155.8845726811967</v>
+        <v>155.8845726811968</v>
       </c>
       <c r="AA17" t="n">
-        <v>-90.00000000000429</v>
+        <v>-90.00000000000179</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>1.117587089538574e-08</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-1.117587089538574e-08</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>8399999.99999997</v>
+        <v>8399999.999999976</v>
       </c>
       <c r="F18" t="n">
-        <v>2099999999.999993</v>
+        <v>2099999999.999994</v>
       </c>
       <c r="G18" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="H18" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="I18" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="N18" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="O18" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="T18" t="n">
-        <v>-90.000000000003</v>
+        <v>-90.00000000000236</v>
       </c>
       <c r="U18" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="Z18" t="n">
-        <v>-90.00000000000894</v>
+        <v>-90.00000000000729</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.60770320892334e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-2.60770320892334e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>8399999.999999994</v>
+        <v>8400000</v>
       </c>
       <c r="F19" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000</v>
       </c>
       <c r="G19" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="H19" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="I19" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="N19" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="O19" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.216893335571513e-12</v>
+        <v>-2.472688720445149e-12</v>
       </c>
       <c r="T19" t="n">
-        <v>311.7691453623973</v>
+        <v>311.7691453623979</v>
       </c>
       <c r="U19" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>179.9999999999977</v>
+        <v>179.9999999999976</v>
       </c>
       <c r="Z19" t="n">
-        <v>311.7691453623971</v>
+        <v>311.7691453623975</v>
       </c>
       <c r="AA19" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>8400000.000000011</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="F20" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
       <c r="G20" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="H20" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="I20" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="N20" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="O20" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>155.8845726811967</v>
+        <v>155.8845726811968</v>
       </c>
       <c r="T20" t="n">
-        <v>270.0000000000006</v>
+        <v>270.0000000000013</v>
       </c>
       <c r="U20" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5196,10 +5196,10 @@
         <v>311.7691453623959</v>
       </c>
       <c r="Z20" t="n">
-        <v>270.0000000000005</v>
+        <v>270.0000000000008</v>
       </c>
       <c r="AA20" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-9.313225746154785e-09</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>9.313225746154785e-09</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>8400000</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="F21" t="n">
-        <v>2100000000</v>
+        <v>2099999999.999999</v>
       </c>
       <c r="G21" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="H21" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="I21" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="N21" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="O21" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>180.0000000000005</v>
+        <v>180.0000000000009</v>
       </c>
       <c r="T21" t="n">
-        <v>311.7691453623955</v>
+        <v>311.7691453623956</v>
       </c>
       <c r="U21" t="n">
-        <v>-90.00000000000894</v>
+        <v>-90.00000000000729</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>270.0000000000005</v>
+        <v>270.0000000000008</v>
       </c>
       <c r="Z21" t="n">
         <v>311.7691453623959</v>
       </c>
       <c r="AA21" t="n">
-        <v>-90.00000000001106</v>
+        <v>-90.00000000000814</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>8399999.999999987</v>
+        <v>8399999.999999978</v>
       </c>
       <c r="F22" t="n">
-        <v>2099999999.999997</v>
+        <v>2099999999.999994</v>
       </c>
       <c r="G22" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="H22" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="I22" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="N22" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="T22" t="n">
-        <v>-90.00000000000894</v>
+        <v>-90.00000000000729</v>
       </c>
       <c r="U22" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="Z22" t="n">
-        <v>-90.00000000001648</v>
+        <v>-90.00000000001415</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>1.862645149230957e-08</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-1.862645149230957e-08</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>8400000.000000006</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="F23" t="n">
-        <v>2100000000.000001</v>
+        <v>2100000000.000002</v>
       </c>
       <c r="G23" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="H23" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="I23" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="N23" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5562,10 +5562,10 @@
         <v>311.7691453623959</v>
       </c>
       <c r="T23" t="n">
-        <v>270.0000000000005</v>
+        <v>270.0000000000008</v>
       </c>
       <c r="U23" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>467.6537180435949</v>
+        <v>467.6537180435951</v>
       </c>
       <c r="Z23" t="n">
-        <v>269.9999999999989</v>
+        <v>269.999999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-1.117587089538574e-08</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>1.117587089538574e-08</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>8400000.000000009</v>
+        <v>8400000.000000006</v>
       </c>
       <c r="F24" t="n">
-        <v>2100000000.000002</v>
+        <v>2100000000.000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-1.30385160446167e-08</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.30385160446167e-08</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>8399999.999999993</v>
+        <v>8399999.999999991</v>
       </c>
       <c r="F25" t="n">
         <v>2099999999.999998</v>
       </c>
       <c r="G25" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="H25" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="I25" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="N25" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="O25" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="T25" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="U25" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="Z25" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="AA25" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5907,13 +5907,13 @@
         <v>2100000000</v>
       </c>
       <c r="G26" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="H26" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="N26" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="O26" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="T26" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="Z26" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>8399999.999999994</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="F27" t="n">
-        <v>2099999999.999999</v>
+        <v>2099999999.999998</v>
       </c>
       <c r="G27" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="H27" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="I27" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="N27" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="O27" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="T27" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="U27" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="Z27" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="AA27" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>2100000000</v>
       </c>
       <c r="G28" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="H28" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="I28" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="N28" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="O28" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="T28" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="U28" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="Z28" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6285,19 +6285,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>8400000</v>
+        <v>8399999.999999989</v>
       </c>
       <c r="F29" t="n">
-        <v>2100000000</v>
+        <v>2099999999.999997</v>
       </c>
       <c r="G29" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="H29" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="I29" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="N29" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="O29" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="T29" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="U29" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="Z29" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="AA29" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6413,16 +6413,16 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>8399999.999999996</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="F30" t="n">
-        <v>2099999999.999999</v>
+        <v>2099999999.999998</v>
       </c>
       <c r="G30" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="H30" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="N30" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="T30" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="Z30" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>5.587935447692871e-09</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>-5.587935447692871e-09</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>8400000.000000015</v>
+        <v>8400000.000000013</v>
       </c>
       <c r="F31" t="n">
-        <v>2100000000.000004</v>
+        <v>2100000000.000003</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="N31" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="O31" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6604,10 +6604,10 @@
         <v>180.0000000000003</v>
       </c>
       <c r="Z31" t="n">
-        <v>-2.486899575160351e-12</v>
+        <v>-2.401634446869139e-12</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>1.172395514004165e-12</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.676380634307861e-08</v>
+        <v>-1.490116119384766e-08</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.676380634307861e-08</v>
+        <v>1.490116119384766e-08</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>8399999.999999987</v>
+        <v>8399999.999999996</v>
       </c>
       <c r="F32" t="n">
-        <v>2099999999.999997</v>
+        <v>2099999999.999999</v>
       </c>
       <c r="G32" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="N32" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="O32" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-45.00000000000006</v>
+        <v>-45.00000000000003</v>
       </c>
       <c r="T32" t="n">
-        <v>51.02520385624574</v>
+        <v>51.02520385624571</v>
       </c>
       <c r="U32" t="n">
-        <v>-58.91883036371802</v>
+        <v>-58.91883036371799</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>134.9999999999997</v>
+        <v>134.9999999999999</v>
       </c>
       <c r="Z32" t="n">
-        <v>51.02520385624755</v>
+        <v>51.02520385624714</v>
       </c>
       <c r="AA32" t="n">
-        <v>-58.91883036371856</v>
+        <v>-58.91883036371783</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>1.862645149230957e-09</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-1.862645149230957e-09</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>8400000.000000009</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="F33" t="n">
-        <v>2100000000.000002</v>
+        <v>2100000000.000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="N33" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="O33" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>201.2461179749813</v>
+        <v>201.2461179749812</v>
       </c>
       <c r="Z33" t="n">
-        <v>-3.240074875066057e-12</v>
+        <v>-2.586375558166765e-12</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-1.862645149230957e-09</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>1.862645149230957e-09</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>8399999.999999981</v>
+        <v>8399999.999999987</v>
       </c>
       <c r="F34" t="n">
-        <v>2099999999.999995</v>
+        <v>2099999999.999997</v>
       </c>
       <c r="G34" t="n">
-        <v>90.00000000000011</v>
+        <v>90.00000000000006</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="N34" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="O34" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>-40.24922359499627</v>
+        <v>-40.24922359499624</v>
       </c>
       <c r="T34" t="n">
-        <v>80.49844718999253</v>
+        <v>80.49844718999248</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>160.9968943799844</v>
+        <v>160.9968943799845</v>
       </c>
       <c r="Z34" t="n">
-        <v>80.4984471899955</v>
+        <v>80.49844718999488</v>
       </c>
       <c r="AA34" t="n">
-        <v>6.127967849993378e-13</v>
+        <v>8.898460371464397e-13</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.048909664154053e-08</v>
+        <v>1.490116119384766e-08</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-2.048909664154053e-08</v>
+        <v>-1.490116119384766e-08</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>8400000.000000013</v>
+        <v>8400000.000000007</v>
       </c>
       <c r="F35" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
       <c r="G35" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>8.093987077986736e-13</v>
       </c>
       <c r="H35" t="n">
-        <v>135.000000000001</v>
+        <v>135.0000000000009</v>
       </c>
       <c r="I35" t="n">
-        <v>77.94228634059888</v>
+        <v>77.94228634059863</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="N35" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="O35" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>135.0000000000013</v>
+        <v>135.0000000000007</v>
       </c>
       <c r="T35" t="n">
-        <v>51.0252038562457</v>
+        <v>51.02520385624623</v>
       </c>
       <c r="U35" t="n">
-        <v>58.91883036371642</v>
+        <v>58.91883036371676</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>315.0000000000016</v>
+        <v>315.0000000000009</v>
       </c>
       <c r="Z35" t="n">
-        <v>51.02520385624136</v>
+        <v>51.0252038562428</v>
       </c>
       <c r="AA35" t="n">
-        <v>58.91883036371632</v>
+        <v>58.91883036371838</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-9.313225746154785e-09</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>9.313225746154785e-09</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>8399999.999999983</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="F36" t="n">
-        <v>2099999999.999996</v>
+        <v>2099999999.999999</v>
       </c>
       <c r="G36" t="n">
-        <v>90.00000000000156</v>
+        <v>90.00000000000072</v>
       </c>
       <c r="H36" t="n">
         <v>134.9999999999986</v>
       </c>
       <c r="I36" t="n">
-        <v>77.94228634060084</v>
+        <v>77.94228634060167</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="N36" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="O36" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>89.99999999999875</v>
+        <v>89.99999999999955</v>
       </c>
       <c r="T36" t="n">
-        <v>102.0504077124906</v>
+        <v>102.0504077124898</v>
       </c>
       <c r="U36" t="n">
-        <v>-117.8376607274379</v>
+        <v>-117.837660727438</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999994</v>
       </c>
       <c r="Z36" t="n">
-        <v>102.0504077124951</v>
+        <v>102.0504077124936</v>
       </c>
       <c r="AA36" t="n">
-        <v>-117.8376607274381</v>
+        <v>-117.8376607274363</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>1.862645149230957e-09</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-1.862645149230957e-09</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>8400000.000000006</v>
+        <v>8400000.000000004</v>
       </c>
       <c r="F37" t="n">
         <v>2100000000.000001</v>
       </c>
       <c r="G37" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>2.329516727335206e-12</v>
       </c>
       <c r="H37" t="n">
-        <v>180.0000000000009</v>
+        <v>180.0000000000008</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="N37" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="O37" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>160.996894379987</v>
+        <v>160.9968943799866</v>
       </c>
       <c r="T37" t="n">
-        <v>80.49844718999019</v>
+        <v>80.4984471899907</v>
       </c>
       <c r="U37" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-8.898460371464397e-13</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>362.2430123549682</v>
+        <v>362.2430123549678</v>
       </c>
       <c r="Z37" t="n">
-        <v>80.49844718998359</v>
+        <v>80.49844718998521</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-5.587935447692871e-09</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>5.587935447692871e-09</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>8399999.999999985</v>
+        <v>8399999.999999993</v>
       </c>
       <c r="F38" t="n">
-        <v>2099999999.999996</v>
+        <v>2099999999.999998</v>
       </c>
       <c r="G38" t="n">
-        <v>90.000000000003</v>
+        <v>90.00000000000236</v>
       </c>
       <c r="H38" t="n">
-        <v>179.9999999999987</v>
+        <v>179.9999999999989</v>
       </c>
       <c r="I38" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>2.411826243744093e-12</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="N38" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="O38" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>120.7476707849862</v>
+        <v>120.7476707849866</v>
       </c>
       <c r="T38" t="n">
-        <v>160.996894379987</v>
+        <v>160.9968943799865</v>
       </c>
       <c r="U38" t="n">
-        <v>-1.526580059720913e-12</v>
+        <v>-2.411826243744093e-12</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>321.9937887599669</v>
+        <v>321.9937887599675</v>
       </c>
       <c r="Z38" t="n">
-        <v>160.9968943799934</v>
+        <v>160.9968943799919</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.021465811082006e-13</v>
+        <v>7.420198735505002e-13</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>8400000.000000013</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="F39" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
       <c r="G39" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.862315955609786e-12</v>
       </c>
       <c r="H39" t="n">
-        <v>270.0000000000013</v>
+        <v>270.0000000000011</v>
       </c>
       <c r="I39" t="n">
-        <v>155.8845726811981</v>
+        <v>155.884572681198</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="N39" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="O39" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>135.0000000000035</v>
+        <v>135.0000000000022</v>
       </c>
       <c r="T39" t="n">
-        <v>255.1260192812264</v>
+        <v>255.1260192812276</v>
       </c>
       <c r="U39" t="n">
-        <v>117.8376607274381</v>
+        <v>117.8376607274363</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>315.0000000000038</v>
+        <v>315.0000000000024</v>
       </c>
       <c r="Z39" t="n">
-        <v>255.1260192812218</v>
+        <v>255.1260192812237</v>
       </c>
       <c r="AA39" t="n">
-        <v>117.8376607274442</v>
+        <v>117.8376607274425</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-1.30385160446167e-08</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>1.30385160446167e-08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>8399999.999999989</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="F40" t="n">
-        <v>2099999999.999997</v>
+        <v>2099999999.999999</v>
       </c>
       <c r="G40" t="n">
-        <v>90.00000000000429</v>
+        <v>90.00000000000179</v>
       </c>
       <c r="H40" t="n">
-        <v>269.9999999999984</v>
+        <v>269.9999999999987</v>
       </c>
       <c r="I40" t="n">
-        <v>155.8845726812006</v>
+        <v>155.8845726812011</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="N40" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="O40" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>89.99999999999589</v>
+        <v>89.99999999999726</v>
       </c>
       <c r="T40" t="n">
-        <v>306.1512231374762</v>
+        <v>306.1512231374753</v>
       </c>
       <c r="U40" t="n">
-        <v>-58.91883036371632</v>
+        <v>-58.91883036371838</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>269.9999999999957</v>
+        <v>269.9999999999972</v>
       </c>
       <c r="Z40" t="n">
-        <v>306.1512231374807</v>
+        <v>306.1512231374792</v>
       </c>
       <c r="AA40" t="n">
-        <v>-58.91883036371006</v>
+        <v>-58.91883036371196</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>1.862645149230957e-09</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-1.862645149230957e-09</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>8400000.000000013</v>
+        <v>8400000.000000009</v>
       </c>
       <c r="F41" t="n">
-        <v>2100000000.000003</v>
+        <v>2100000000.000002</v>
       </c>
       <c r="G41" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>7.292197765110538e-12</v>
       </c>
       <c r="H41" t="n">
-        <v>360.0000000000013</v>
+        <v>360.0000000000012</v>
       </c>
       <c r="I41" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="N41" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>321.9937887599748</v>
+        <v>321.993788759974</v>
       </c>
       <c r="T41" t="n">
-        <v>160.9968943799774</v>
+        <v>160.9968943799789</v>
       </c>
       <c r="U41" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-7.420198735505002e-13</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>523.2399067349562</v>
+        <v>523.2399067349553</v>
       </c>
       <c r="Z41" t="n">
-        <v>160.9968943799691</v>
+        <v>160.9968943799713</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-9.313225746154785e-09</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>9.313225746154785e-09</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>8399999.999999983</v>
+        <v>8399999.999999989</v>
       </c>
       <c r="F42" t="n">
-        <v>2099999999.999996</v>
+        <v>2099999999.999997</v>
       </c>
       <c r="G42" t="n">
-        <v>90.00000000000894</v>
+        <v>90.00000000000729</v>
       </c>
       <c r="H42" t="n">
-        <v>359.9999999999981</v>
+        <v>359.9999999999984</v>
       </c>
       <c r="I42" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>1.909017094802782e-12</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="N42" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>281.7445651649678</v>
+        <v>281.7445651649688</v>
       </c>
       <c r="T42" t="n">
-        <v>241.4953415699844</v>
+        <v>241.4953415699831</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.610967014838157e-12</v>
+        <v>-1.909017094802782e-12</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>482.9906831399485</v>
+        <v>482.9906831399496</v>
       </c>
       <c r="Z42" t="n">
-        <v>241.4953415699927</v>
+        <v>241.4953415699907</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>1.30385160446167e-08</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>-1.30385160446167e-08</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>8399999.999999996</v>
+        <v>8400000.000000006</v>
       </c>
       <c r="F43" t="n">
-        <v>2099999999.999999</v>
+        <v>2100000000.000001</v>
       </c>
       <c r="G43" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>8.25034530002525e-12</v>
       </c>
       <c r="H43" t="n">
-        <v>405.0000000000011</v>
+        <v>405.0000000000013</v>
       </c>
       <c r="I43" t="n">
-        <v>77.94228634059863</v>
+        <v>77.94228634059871</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>90.00000000001648</v>
+        <v>90.00000000001415</v>
       </c>
       <c r="N43" t="n">
-        <v>539.9999999999978</v>
+        <v>539.999999999998</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>270.0000000000067</v>
+        <v>270.0000000000055</v>
       </c>
       <c r="T43" t="n">
-        <v>306.1512231374682</v>
+        <v>306.1512231374699</v>
       </c>
       <c r="U43" t="n">
-        <v>58.91883036372453</v>
+        <v>58.91883036372276</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>450.0000000000067</v>
+        <v>450.0000000000056</v>
       </c>
       <c r="Z43" t="n">
-        <v>306.1512231374633</v>
+        <v>306.1512231374647</v>
       </c>
       <c r="AA43" t="n">
-        <v>58.91883036372874</v>
+        <v>58.91883036372722</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>8400000.000000006</v>
+        <v>8399999.999999994</v>
       </c>
       <c r="F44" t="n">
-        <v>2100000000.000001</v>
+        <v>2099999999.999999</v>
       </c>
       <c r="G44" t="n">
-        <v>90.00000000001106</v>
+        <v>90.00000000000814</v>
       </c>
       <c r="H44" t="n">
-        <v>404.9999999999985</v>
+        <v>404.9999999999987</v>
       </c>
       <c r="I44" t="n">
-        <v>77.94228634060087</v>
+        <v>77.94228634060116</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>1.421950808161317e-11</v>
       </c>
       <c r="N44" t="n">
-        <v>540.0000000000015</v>
+        <v>540.0000000000016</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>224.9999999999928</v>
+        <v>224.9999999999942</v>
       </c>
       <c r="T44" t="n">
-        <v>357.1764269937257</v>
+        <v>357.1764269937244</v>
       </c>
       <c r="U44" t="n">
-        <v>6.188827228470473e-12</v>
+        <v>4.071409875905374e-12</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>404.9999999999929</v>
+        <v>404.9999999999941</v>
       </c>
       <c r="Z44" t="n">
-        <v>357.1764269937301</v>
+        <v>357.1764269937289</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.080870108381344e-11</v>
+        <v>9.30885316128981e-12</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_temperature.xlsx
+++ b/outputs/validation_truss_temperature.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="F4" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="G4" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>155.8845726811995</v>
+        <v>0.00155884572681199</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="F5" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="F6" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="F7" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="G7" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>201.2461179749813</v>
+        <v>0.002012461179749812</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="F8" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>311.7691453623987</v>
+        <v>0.003117691453623978</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="F9" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>324.4996147917596</v>
+        <v>0.00324499614791759</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="F10" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="F11" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="G11" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>371.0795063055898</v>
+        <v>0.003710795063055898</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="F12" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="G12" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>412.4318125460265</v>
+        <v>0.004124318125460252</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="F13" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>422.1374183841098</v>
+        <v>0.004221374183841089</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="F14" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="F15" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>547.4486277268403</v>
+        <v>0.005474486277268402</v>
       </c>
     </row>
   </sheetData>
@@ -1035,13 +1035,13 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>547.4486277268403</v>
+        <v>0.005474486277268402</v>
       </c>
       <c r="D2" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="E2" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="D3" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="E3" t="n">
-        <v>539.9999999999978</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.00155884572681198</v>
       </c>
     </row>
     <row r="4">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="D4" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="E4" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>155.8845726812006</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="D5" t="n">
-        <v>90.00000000000429</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="E5" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>155.8845726812006</v>
+        <v>0.001558845726811987</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.421438694000244e-08</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.313225746154785e-08</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.142041921615601e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.080334186553955e-07</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>1.955777406692505e-08</v>
+        <v>1.27897692436818e-13</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>30.00000000000016</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>8400000.000000043</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I2" t="n">
-        <v>2100000000.000011</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>155.8845726811995</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="G3" t="n">
-        <v>30.00000000000011</v>
+        <v>0.0003</v>
       </c>
       <c r="H3" t="n">
-        <v>8400000.000000032</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2100000000.000008</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>89.99999999999999</v>
+        <v>0.0009000000000000005</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>8399999.999999998</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="I4" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>155.8845726811991</v>
+        <v>0.001558845726811989</v>
       </c>
       <c r="G5" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999994</v>
       </c>
       <c r="I5" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>179.9999999999999</v>
+        <v>0.0018</v>
       </c>
       <c r="G6" t="n">
-        <v>29.99999999999999</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>180.0000000000004</v>
+        <v>0.0018</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00000000000006</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>8400000.000000017</v>
+        <v>83.99999999999997</v>
       </c>
       <c r="I7" t="n">
-        <v>2100000000.000004</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>180</v>
+        <v>0.001800000000000003</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>0.0003000000000000005</v>
       </c>
       <c r="H8" t="n">
-        <v>8400000</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="I8" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000004</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>155.8845726811988</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="G9" t="n">
-        <v>29.99999999999997</v>
+        <v>0.0002999999999999995</v>
       </c>
       <c r="H9" t="n">
-        <v>8399999.999999991</v>
+        <v>83.99999999999986</v>
       </c>
       <c r="I9" t="n">
-        <v>2099999999.999998</v>
+        <v>20999.99999999996</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>89.99999999999994</v>
+        <v>0.0008999999999999987</v>
       </c>
       <c r="G10" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0002999999999999995</v>
       </c>
       <c r="H10" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999987</v>
       </c>
       <c r="I10" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999997</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>180.0000000000002</v>
+        <v>0.001799999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>30.00000000000003</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>8400000.000000007</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>2100000000.000002</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>155.8845726811988</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="G12" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003</v>
       </c>
       <c r="H12" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="I12" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="G13" t="n">
-        <v>29.99999999999979</v>
+        <v>0.0003</v>
       </c>
       <c r="H13" t="n">
-        <v>8399999.99999994</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2099999999.999985</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>155.8845726811984</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="G14" t="n">
-        <v>29.99999999999989</v>
+        <v>0.0002999999999999994</v>
       </c>
       <c r="H14" t="n">
-        <v>8399999.99999997</v>
+        <v>83.99999999999984</v>
       </c>
       <c r="I14" t="n">
-        <v>2099999999.999993</v>
+        <v>20999.99999999996</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>89.99999999999996</v>
+        <v>0.0009000000000000002</v>
       </c>
       <c r="G15" t="n">
-        <v>29.99999999999999</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>155.8845726811988</v>
+        <v>0.001558845726811988</v>
       </c>
       <c r="G16" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I16" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>179.9999999999999</v>
+        <v>0.0018</v>
       </c>
       <c r="G17" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003</v>
       </c>
       <c r="H17" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>179.9999999999994</v>
+        <v>0.001800000000000003</v>
       </c>
       <c r="G18" t="n">
-        <v>29.9999999999999</v>
+        <v>0.0003000000000000005</v>
       </c>
       <c r="H18" t="n">
-        <v>8399999.99999997</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="I18" t="n">
-        <v>2099999999.999993</v>
+        <v>21000.00000000004</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>179.9999999999999</v>
+        <v>0.0018</v>
       </c>
       <c r="G19" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003</v>
       </c>
       <c r="H19" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="I19" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>155.8845726811992</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="G20" t="n">
-        <v>30.00000000000004</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>8400000.000000011</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I20" t="n">
-        <v>2100000000.000003</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>0.0009000000000000002</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>8400000</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>179.9999999999997</v>
+        <v>0.001800000000000003</v>
       </c>
       <c r="G22" t="n">
-        <v>29.99999999999995</v>
+        <v>0.0003000000000000004</v>
       </c>
       <c r="H22" t="n">
-        <v>8399999.999999987</v>
+        <v>84.00000000000011</v>
       </c>
       <c r="I22" t="n">
-        <v>2099999999.999997</v>
+        <v>21000.00000000003</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>155.8845726811991</v>
+        <v>0.001558845726811988</v>
       </c>
       <c r="G23" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I23" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>30.00000000000004</v>
+        <v>0.0003000000000000003</v>
       </c>
       <c r="H24" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="I24" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000002</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>89.99999999999993</v>
+        <v>0.0009000000000000006</v>
       </c>
       <c r="G25" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="I25" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>90.00000000000003</v>
+        <v>0.0009</v>
       </c>
       <c r="G26" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0003</v>
       </c>
       <c r="H26" t="n">
-        <v>8400000.000000002</v>
+        <v>84</v>
       </c>
       <c r="I26" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="27">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>89.99999999999994</v>
+        <v>0.0009000000000000004</v>
       </c>
       <c r="G27" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>8399999.999999994</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I27" t="n">
-        <v>2099999999.999999</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2081,16 +2081,16 @@
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>0.0008999999999999997</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>8400000</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="I28" t="n">
-        <v>2100000000</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2112,16 +2112,16 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>90</v>
+        <v>0.0009000000000000005</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H29" t="n">
-        <v>8400000</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="I29" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2143,16 +2143,16 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>89.99999999999997</v>
+        <v>0.0009000000000000003</v>
       </c>
       <c r="G30" t="n">
-        <v>29.99999999999999</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I30" t="n">
-        <v>2099999999.999999</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
       <c r="G31" t="n">
-        <v>30.00000000000005</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>8400000.000000015</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2100000000.000004</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>179.9999999999997</v>
+        <v>0.001799999999999998</v>
       </c>
       <c r="G32" t="n">
-        <v>29.99999999999995</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H32" t="n">
-        <v>8399999.999999987</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I32" t="n">
-        <v>2099999999.999997</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>201.2461179749813</v>
+        <v>0.002012461179749812</v>
       </c>
       <c r="G33" t="n">
-        <v>30.00000000000003</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H33" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="I33" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>201.2461179749806</v>
+        <v>0.00201246117974981</v>
       </c>
       <c r="G34" t="n">
-        <v>29.99999999999993</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>8399999.999999981</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>2099999999.999995</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
       <c r="G35" t="n">
-        <v>30.00000000000005</v>
+        <v>0.0003</v>
       </c>
       <c r="H35" t="n">
-        <v>8400000.000000013</v>
+        <v>84</v>
       </c>
       <c r="I35" t="n">
-        <v>2100000000.000003</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>179.9999999999997</v>
+        <v>0.001799999999999998</v>
       </c>
       <c r="G36" t="n">
-        <v>29.99999999999994</v>
+        <v>0.0002999999999999996</v>
       </c>
       <c r="H36" t="n">
-        <v>8399999.999999983</v>
+        <v>83.99999999999989</v>
       </c>
       <c r="I36" t="n">
-        <v>2099999999.999996</v>
+        <v>20999.99999999997</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>201.2461179749812</v>
+        <v>0.002012461179749812</v>
       </c>
       <c r="G37" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H37" t="n">
-        <v>8400000.000000006</v>
+        <v>84.00000000000007</v>
       </c>
       <c r="I37" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000002</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>201.2461179749807</v>
+        <v>0.002012461179749811</v>
       </c>
       <c r="G38" t="n">
-        <v>29.99999999999994</v>
+        <v>0.0003</v>
       </c>
       <c r="H38" t="n">
-        <v>8399999.999999985</v>
+        <v>84</v>
       </c>
       <c r="I38" t="n">
-        <v>2099999999.999996</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>180.0000000000003</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>30.00000000000005</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>8400000.000000013</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I39" t="n">
-        <v>2100000000.000003</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>179.9999999999998</v>
+        <v>0.001799999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>29.99999999999996</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H40" t="n">
-        <v>8399999.999999989</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I40" t="n">
-        <v>2099999999.999997</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>201.2461179749814</v>
+        <v>0.002012461179749813</v>
       </c>
       <c r="G41" t="n">
-        <v>30.00000000000004</v>
+        <v>0.0003000000000000003</v>
       </c>
       <c r="H41" t="n">
-        <v>8400000.000000013</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="I41" t="n">
-        <v>2100000000.000003</v>
+        <v>21000.00000000002</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>201.2461179749807</v>
+        <v>0.00201246117974981</v>
       </c>
       <c r="G42" t="n">
-        <v>29.99999999999994</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>8399999.999999983</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>2099999999.999996</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001799999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>29.99999999999999</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>8399999.999999996</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="I43" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>180.0000000000001</v>
+        <v>0.0018</v>
       </c>
       <c r="G44" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0003</v>
       </c>
       <c r="H44" t="n">
-        <v>8400000.000000006</v>
+        <v>84</v>
       </c>
       <c r="I44" t="n">
-        <v>2100000000.000001</v>
+        <v>21000</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>8400000.000000043</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F2" t="n">
-        <v>2100000000.000011</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="N2" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2.968575733106793e-12</v>
+        <v>-3.29262008803703e-18</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4.656612873077393e-08</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>4.656612873077393e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>8400000.000000032</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2100000000.000008</v>
+        <v>21000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="N3" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="O3" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>155.8845726811995</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>2.818925648462312e-18</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.627271987320841e-12</v>
+        <v>-4.753737175074203e-18</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3.166496753692627e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.166496753692627e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>8399999.999999998</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="F4" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H4" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.008970684779342e-12</v>
+        <v>2.710505431213761e-18</v>
       </c>
       <c r="T4" t="n">
-        <v>155.8845726811995</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="U4" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>90.00000000000099</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.8845726811995</v>
+        <v>0.001558845726811989</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999994</v>
       </c>
       <c r="F5" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H5" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I5" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="N5" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>155.8845726811995</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="T5" t="n">
-        <v>1.023181539494544e-12</v>
+        <v>2.818925648462312e-18</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.627271987320841e-12</v>
+        <v>-4.753737175074203e-18</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>311.7691453623986</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>2.818925648462312e-18</v>
       </c>
       <c r="AA5" t="n">
-        <v>-4.352044038901301e-12</v>
+        <v>-1.273119217156146e-17</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-5.587935447692871e-09</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.587935447692871e-09</v>
+        <v>-9.947598300641403e-14</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G6" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H6" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="N6" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>89.99999999999994</v>
+        <v>0.0008999999999999976</v>
       </c>
       <c r="T6" t="n">
-        <v>155.8845726812001</v>
+        <v>0.001558845726811992</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.968575733106793e-12</v>
+        <v>-3.29262008803703e-18</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>269.9999999999999</v>
+        <v>0.002699999999999998</v>
       </c>
       <c r="Z6" t="n">
-        <v>155.8845726812005</v>
+        <v>0.001558845726811991</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.352044038901301e-12</v>
+        <v>-1.273119217156146e-17</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>8400000.000000017</v>
+        <v>83.99999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>2100000000.000004</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H7" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="N7" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.968575733106793e-12</v>
+        <v>-3.29262008803703e-18</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8.931538245898027e-12</v>
+        <v>-3.519396974980317e-18</v>
       </c>
       <c r="AA7" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-2.048909664154053e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.048909664154053e-08</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>8400000</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="F8" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000004</v>
       </c>
       <c r="G8" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H8" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="N8" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>2.602085213965211e-18</v>
       </c>
       <c r="T8" t="n">
-        <v>311.7691453623986</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="U8" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>180.0000000000014</v>
+        <v>0.001800000000000006</v>
       </c>
       <c r="Z8" t="n">
-        <v>311.7691453623986</v>
+        <v>0.003117691453623977</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-1.4210854715202e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>8399999.999999991</v>
+        <v>83.99999999999986</v>
       </c>
       <c r="F9" t="n">
-        <v>2099999999.999998</v>
+        <v>20999.99999999996</v>
       </c>
       <c r="G9" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H9" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="N9" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="O9" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>155.8845726812005</v>
+        <v>0.001558845726811991</v>
       </c>
       <c r="T9" t="n">
-        <v>269.9999999999999</v>
+        <v>0.002699999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>311.7691453623993</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="Z9" t="n">
-        <v>269.9999999999998</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>1.84741111297626e-13</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-1.84741111297626e-13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999987</v>
       </c>
       <c r="F10" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999997</v>
       </c>
       <c r="G10" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H10" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="I10" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="N10" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="O10" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001799999999999995</v>
       </c>
       <c r="T10" t="n">
-        <v>311.7691453623995</v>
+        <v>0.003117691453623983</v>
       </c>
       <c r="U10" t="n">
-        <v>-8.931538245898027e-12</v>
+        <v>-3.519396974980317e-18</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>269.9999999999998</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="Z10" t="n">
-        <v>311.7691453623994</v>
+        <v>0.003117691453623979</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.105109697137119e-11</v>
+        <v>-6.620434362867334e-18</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-1.4210854715202e-13</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>8400000.000000007</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="F11" t="n">
-        <v>2100000000.000002</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H11" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N11" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.931538245898027e-12</v>
+        <v>-3.519396974980317e-18</v>
       </c>
       <c r="U11" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.651056362690877e-11</v>
+        <v>3.910240474061865e-18</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G12" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="H12" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="I12" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N12" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>311.7691453623993</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="T12" t="n">
-        <v>269.9999999999998</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="U12" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>467.6537180435981</v>
+        <v>0.004676537180435968</v>
       </c>
       <c r="Z12" t="n">
-        <v>270.0000000000007</v>
+        <v>0.0027</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>8399999.99999994</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2099999999.999985</v>
+        <v>21000</v>
       </c>
       <c r="G13" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N13" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="O13" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-90.00000000000011</v>
+        <v>-0.000900000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="Z13" t="n">
-        <v>-90.000000000003</v>
+        <v>-0.0009000000000000032</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>5.587935447692871e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-5.587935447692871e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>8399999.99999997</v>
+        <v>83.99999999999984</v>
       </c>
       <c r="F14" t="n">
-        <v>2099999999.999993</v>
+        <v>20999.99999999996</v>
       </c>
       <c r="G14" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="N14" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-90.00000000000011</v>
+        <v>-0.000900000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>155.8845726811984</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.890043677121866e-12</v>
+        <v>7.155734338404329e-18</v>
       </c>
       <c r="AA14" t="n">
-        <v>-90.00000000000156</v>
+        <v>-0.0009000000000000054</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.84741111297626e-13</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.84741111297626e-13</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G15" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="H15" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N15" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="O15" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.904254531837068e-12</v>
+        <v>7.047314121155779e-18</v>
       </c>
       <c r="T15" t="n">
-        <v>155.8845726811984</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="U15" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>89.99999999999805</v>
+        <v>0.0009000000000000072</v>
       </c>
       <c r="Z15" t="n">
-        <v>155.8845726811986</v>
+        <v>0.001558845726811985</v>
       </c>
       <c r="AA15" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F16" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G16" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="H16" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N16" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>155.8845726811984</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.890043677121866e-12</v>
+        <v>7.155734338404329e-18</v>
       </c>
       <c r="U16" t="n">
-        <v>-90.00000000000156</v>
+        <v>-0.0009000000000000054</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>311.7691453623972</v>
+        <v>0.003117691453623975</v>
       </c>
       <c r="Z16" t="n">
-        <v>-2.188471626141109e-12</v>
+        <v>8.456776945386935e-18</v>
       </c>
       <c r="AA16" t="n">
-        <v>-90.00000000000429</v>
+        <v>-0.0009000000000000131</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-9.947598300641403e-14</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G17" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="H17" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="I17" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N17" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>90.0000000000007</v>
+        <v>0.0008999999999999925</v>
       </c>
       <c r="T17" t="n">
-        <v>155.8845726811971</v>
+        <v>0.001558845726811994</v>
       </c>
       <c r="U17" t="n">
-        <v>-90.000000000003</v>
+        <v>-0.0009000000000000032</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>270.0000000000006</v>
+        <v>0.002699999999999992</v>
       </c>
       <c r="Z17" t="n">
-        <v>155.8845726811967</v>
+        <v>0.001558845726811995</v>
       </c>
       <c r="AA17" t="n">
-        <v>-90.00000000000429</v>
+        <v>-0.0009000000000000131</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>8399999.99999997</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="F18" t="n">
-        <v>2099999999.999993</v>
+        <v>21000.00000000004</v>
       </c>
       <c r="G18" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="H18" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="I18" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N18" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O18" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="T18" t="n">
-        <v>-90.000000000003</v>
+        <v>-0.0009000000000000032</v>
       </c>
       <c r="U18" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="Z18" t="n">
-        <v>-90.00000000000894</v>
+        <v>-0.0009000000000000031</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.60770320892334e-08</v>
+        <v>-1.27897692436818e-13</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-2.60770320892334e-08</v>
+        <v>1.27897692436818e-13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G19" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="H19" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N19" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O19" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.216893335571513e-12</v>
+        <v>8.239936510889834e-18</v>
       </c>
       <c r="T19" t="n">
-        <v>311.7691453623973</v>
+        <v>0.003117691453623975</v>
       </c>
       <c r="U19" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>179.9999999999977</v>
+        <v>0.001800000000000008</v>
       </c>
       <c r="Z19" t="n">
-        <v>311.7691453623971</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="AA19" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>8400000.000000011</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F20" t="n">
-        <v>2100000000.000003</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="H20" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N20" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O20" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>155.8845726811967</v>
+        <v>0.001558845726811995</v>
       </c>
       <c r="T20" t="n">
-        <v>270.0000000000006</v>
+        <v>0.002699999999999992</v>
       </c>
       <c r="U20" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>311.7691453623959</v>
+        <v>0.003117691453623985</v>
       </c>
       <c r="Z20" t="n">
-        <v>270.0000000000005</v>
+        <v>0.002699999999999995</v>
       </c>
       <c r="AA20" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-9.313225746154785e-09</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>9.313225746154785e-09</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>8400000</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
       <c r="G21" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="H21" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="I21" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N21" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O21" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>180.0000000000005</v>
+        <v>0.001799999999999995</v>
       </c>
       <c r="T21" t="n">
-        <v>311.7691453623955</v>
+        <v>0.003117691453623986</v>
       </c>
       <c r="U21" t="n">
-        <v>-90.00000000000894</v>
+        <v>-0.0009000000000000031</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>270.0000000000005</v>
+        <v>0.002699999999999995</v>
       </c>
       <c r="Z21" t="n">
-        <v>311.7691453623959</v>
+        <v>0.003117691453623985</v>
       </c>
       <c r="AA21" t="n">
-        <v>-90.00000000001106</v>
+        <v>-0.0009000000000000071</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>8399999.999999987</v>
+        <v>84.00000000000011</v>
       </c>
       <c r="F22" t="n">
-        <v>2099999999.999997</v>
+        <v>21000.00000000003</v>
       </c>
       <c r="G22" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="H22" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="I22" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N22" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="T22" t="n">
-        <v>-90.00000000000894</v>
+        <v>-0.0009000000000000031</v>
       </c>
       <c r="U22" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="Z22" t="n">
-        <v>-90.00000000001648</v>
+        <v>-0.0008999999999999964</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F23" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G23" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="H23" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="I23" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N23" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>311.7691453623959</v>
+        <v>0.003117691453623985</v>
       </c>
       <c r="T23" t="n">
-        <v>270.0000000000005</v>
+        <v>0.002699999999999995</v>
       </c>
       <c r="U23" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>467.6537180435949</v>
+        <v>0.004676537180435973</v>
       </c>
       <c r="Z23" t="n">
-        <v>269.9999999999989</v>
+        <v>0.002700000000000003</v>
       </c>
       <c r="AA23" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="F24" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000002</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-1.30385160446167e-08</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.30385160446167e-08</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="F25" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H25" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I25" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="N25" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="T25" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="Z25" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>8400000.000000002</v>
+        <v>84</v>
       </c>
       <c r="F26" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
       <c r="G26" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H26" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N26" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="O26" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="T26" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="Z26" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>8399999.999999994</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F27" t="n">
-        <v>2099999999.999999</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H27" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N27" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="T27" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="Z27" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6157,19 +6157,19 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>8400000</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="F28" t="n">
-        <v>2100000000</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H28" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="I28" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N28" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O28" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="T28" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="U28" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="Z28" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -6285,19 +6285,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>8400000</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="F29" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="H29" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="I29" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N29" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O29" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="T29" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="U29" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="Z29" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="AA29" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6413,16 +6413,16 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F30" t="n">
-        <v>2099999999.999999</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="H30" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N30" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="T30" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="Z30" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>8400000.000000015</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>2100000000.000004</v>
+        <v>21000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="N31" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
       <c r="Z31" t="n">
-        <v>-2.486899575160351e-12</v>
+        <v>1.409462824231156e-18</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-9.324138683375338e-18</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.676380634307861e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.676380634307861e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>8399999.999999987</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F32" t="n">
-        <v>2099999999.999997</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G32" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="N32" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="O32" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-45.00000000000006</v>
+        <v>-0.0004500000000000005</v>
       </c>
       <c r="T32" t="n">
-        <v>51.02520385624574</v>
+        <v>0.0005102520385624573</v>
       </c>
       <c r="U32" t="n">
-        <v>-58.91883036371802</v>
+        <v>-0.0005891883036371801</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>134.9999999999997</v>
+        <v>0.001349999999999998</v>
       </c>
       <c r="Z32" t="n">
-        <v>51.02520385624755</v>
+        <v>0.0005102520385624617</v>
       </c>
       <c r="AA32" t="n">
-        <v>-58.91883036371856</v>
+        <v>-0.0005891883036371809</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="F33" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N33" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="O33" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>201.2461179749813</v>
+        <v>0.002012461179749812</v>
       </c>
       <c r="Z33" t="n">
-        <v>-3.240074875066057e-12</v>
+        <v>-3.035766082959412e-18</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>8399999.999999981</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>2099999999.999995</v>
+        <v>21000</v>
       </c>
       <c r="G34" t="n">
-        <v>90.00000000000011</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="N34" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>-40.24922359499627</v>
+        <v>-0.0004024922359499625</v>
       </c>
       <c r="T34" t="n">
-        <v>80.49844718999253</v>
+        <v>0.0008049844718999251</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>160.9968943799844</v>
+        <v>0.001609968943799848</v>
       </c>
       <c r="Z34" t="n">
-        <v>80.4984471899955</v>
+        <v>0.0008049844718999276</v>
       </c>
       <c r="AA34" t="n">
-        <v>6.127967849993378e-13</v>
+        <v>3.21025446370383e-18</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.048909664154053e-08</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-2.048909664154053e-08</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>8400000.000000013</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
-        <v>2100000000.000003</v>
+        <v>21000</v>
       </c>
       <c r="G35" t="n">
-        <v>1.627271987320841e-12</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H35" t="n">
-        <v>135.000000000001</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I35" t="n">
-        <v>77.94228634059888</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N35" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>135.0000000000013</v>
+        <v>0.001350000000000003</v>
       </c>
       <c r="T35" t="n">
-        <v>51.0252038562457</v>
+        <v>0.0005102520385624563</v>
       </c>
       <c r="U35" t="n">
-        <v>58.91883036371642</v>
+        <v>0.0005891883036371746</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>315.0000000000016</v>
+        <v>0.003150000000000003</v>
       </c>
       <c r="Z35" t="n">
-        <v>51.02520385624136</v>
+        <v>0.0005102520385624543</v>
       </c>
       <c r="AA35" t="n">
-        <v>58.91883036371632</v>
+        <v>0.0005891883036371637</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>8399999.999999983</v>
+        <v>83.99999999999989</v>
       </c>
       <c r="F36" t="n">
-        <v>2099999999.999996</v>
+        <v>20999.99999999997</v>
       </c>
       <c r="G36" t="n">
-        <v>90.00000000000156</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="H36" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>77.94228634060084</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="N36" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>89.99999999999875</v>
+        <v>0.0008999999999999949</v>
       </c>
       <c r="T36" t="n">
-        <v>102.0504077124906</v>
+        <v>0.001020504077124921</v>
       </c>
       <c r="U36" t="n">
-        <v>-117.8376607274379</v>
+        <v>-0.001178376607274357</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="Z36" t="n">
-        <v>102.0504077124951</v>
+        <v>0.001020504077124923</v>
       </c>
       <c r="AA36" t="n">
-        <v>-117.8376607274381</v>
+        <v>-0.001178376607274365</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-9.947598300641403e-14</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>8400000.000000006</v>
+        <v>84.00000000000007</v>
       </c>
       <c r="F37" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.968575733106793e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H37" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N37" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O37" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>160.996894379987</v>
+        <v>0.001609968943799851</v>
       </c>
       <c r="T37" t="n">
-        <v>80.49844718999019</v>
+        <v>0.0008049844718999217</v>
       </c>
       <c r="U37" t="n">
-        <v>-6.127967849993378e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>362.2430123549682</v>
+        <v>0.003622430123549663</v>
       </c>
       <c r="Z37" t="n">
-        <v>80.49844718998359</v>
+        <v>0.0008049844718999229</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-5.587935447692871e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>5.587935447692871e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>8399999.999999985</v>
+        <v>84</v>
       </c>
       <c r="F38" t="n">
-        <v>2099999999.999996</v>
+        <v>21000</v>
       </c>
       <c r="G38" t="n">
-        <v>90.000000000003</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="H38" t="n">
-        <v>179.9999999999987</v>
+        <v>0.0018</v>
       </c>
       <c r="I38" t="n">
-        <v>1.526580059720913e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="N38" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="O38" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>120.7476707849862</v>
+        <v>0.001207476707849885</v>
       </c>
       <c r="T38" t="n">
-        <v>160.996894379987</v>
+        <v>0.001609968943799851</v>
       </c>
       <c r="U38" t="n">
-        <v>-1.526580059720913e-12</v>
+        <v>8.564521398736833e-18</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>321.9937887599669</v>
+        <v>0.003219937887599696</v>
       </c>
       <c r="Z38" t="n">
-        <v>160.9968943799934</v>
+        <v>0.001609968943799852</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.021465811082006e-13</v>
+        <v>6.421903002751408e-18</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>8400000.000000013</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F39" t="n">
-        <v>2100000000.000003</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>4.352044038901301e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H39" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>155.8845726811981</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N39" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O39" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>135.0000000000035</v>
+        <v>0.001350000000000008</v>
       </c>
       <c r="T39" t="n">
-        <v>255.1260192812264</v>
+        <v>0.002551260192812276</v>
       </c>
       <c r="U39" t="n">
-        <v>117.8376607274381</v>
+        <v>0.001178376607274365</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>315.0000000000038</v>
+        <v>0.003150000000000009</v>
       </c>
       <c r="Z39" t="n">
-        <v>255.1260192812218</v>
+        <v>0.002551260192812278</v>
       </c>
       <c r="AA39" t="n">
-        <v>117.8376607274442</v>
+        <v>0.001178376607274358</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>8399999.999999989</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F40" t="n">
-        <v>2099999999.999997</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G40" t="n">
-        <v>90.00000000000429</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="H40" t="n">
-        <v>269.9999999999984</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>155.8845726812006</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="N40" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="O40" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>89.99999999999589</v>
+        <v>0.0008999999999999977</v>
       </c>
       <c r="T40" t="n">
-        <v>306.1512231374762</v>
+        <v>0.003061512231374744</v>
       </c>
       <c r="U40" t="n">
-        <v>-58.91883036371632</v>
+        <v>-0.0005891883036371637</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>269.9999999999957</v>
+        <v>0.002699999999999996</v>
       </c>
       <c r="Z40" t="n">
-        <v>306.1512231374807</v>
+        <v>0.003061512231374739</v>
       </c>
       <c r="AA40" t="n">
-        <v>-58.91883036371006</v>
+        <v>-0.0005891883036371709</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>7.105427357601002e-14</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-7.105427357601002e-14</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>8400000.000000013</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="F41" t="n">
-        <v>2100000000.000003</v>
+        <v>21000.00000000002</v>
       </c>
       <c r="G41" t="n">
-        <v>8.931538245898027e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H41" t="n">
-        <v>360.0000000000013</v>
+        <v>0.0036</v>
       </c>
       <c r="I41" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N41" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>321.9937887599748</v>
+        <v>0.003219937887599699</v>
       </c>
       <c r="T41" t="n">
-        <v>160.9968943799774</v>
+        <v>0.001609968943799845</v>
       </c>
       <c r="U41" t="n">
-        <v>-9.021465811082006e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>523.2399067349562</v>
+        <v>0.005232399067349512</v>
       </c>
       <c r="Z41" t="n">
-        <v>160.9968943799691</v>
+        <v>0.001609968943799854</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>8399999.999999983</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>2099999999.999996</v>
+        <v>21000</v>
       </c>
       <c r="G42" t="n">
-        <v>90.00000000000894</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="H42" t="n">
-        <v>359.9999999999981</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="I42" t="n">
-        <v>1.610967014838157e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N42" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>281.7445651649678</v>
+        <v>0.002817445651649736</v>
       </c>
       <c r="T42" t="n">
-        <v>241.4953415699844</v>
+        <v>0.002414953415699777</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.610967014838157e-12</v>
+        <v>7.708358245815531e-18</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>482.9906831399485</v>
+        <v>0.004829906831399547</v>
       </c>
       <c r="Z42" t="n">
-        <v>241.4953415699927</v>
+        <v>0.002414953415699769</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>7.105427357601002e-14</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>-7.105427357601002e-14</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>8399999.999999996</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="F43" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>1.105109697137119e-11</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="H43" t="n">
-        <v>405.0000000000011</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="I43" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>90.00000000001648</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N43" t="n">
-        <v>539.9999999999978</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>270.0000000000067</v>
+        <v>0.002700000000000003</v>
       </c>
       <c r="T43" t="n">
-        <v>306.1512231374682</v>
+        <v>0.003061512231374732</v>
       </c>
       <c r="U43" t="n">
-        <v>58.91883036372453</v>
+        <v>0.0005891883036371796</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>450.0000000000067</v>
+        <v>0.004500000000000002</v>
       </c>
       <c r="Z43" t="n">
-        <v>306.1512231374633</v>
+        <v>0.003061512231374746</v>
       </c>
       <c r="AA43" t="n">
-        <v>58.91883036372874</v>
+        <v>0.0005891883036371771</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>8400000.000000006</v>
+        <v>84</v>
       </c>
       <c r="F44" t="n">
-        <v>2100000000.000001</v>
+        <v>21000</v>
       </c>
       <c r="G44" t="n">
-        <v>90.00000000001106</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="H44" t="n">
-        <v>404.9999999999985</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="I44" t="n">
-        <v>77.94228634060087</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.651056362690877e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N44" t="n">
-        <v>540.0000000000015</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>224.9999999999928</v>
+        <v>0.002250000000000002</v>
       </c>
       <c r="T44" t="n">
-        <v>357.1764269937257</v>
+        <v>0.0035717642699372</v>
       </c>
       <c r="U44" t="n">
-        <v>6.188827228470473e-12</v>
+        <v>1.008308020411519e-17</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>404.9999999999929</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="Z44" t="n">
-        <v>357.1764269937301</v>
+        <v>0.003571764269937195</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.080870108381344e-11</v>
+        <v>-2.559853279695501e-18</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_temperature.xlsx
+++ b/outputs/validation_truss_temperature.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="F4" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="G4" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>155.8845726811993</v>
+        <v>0.00155884572681199</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="F5" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="F6" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="F7" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="G7" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>201.2461179749812</v>
+        <v>0.002012461179749812</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="F8" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>311.7691453623984</v>
+        <v>0.003117691453623978</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="F9" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>324.4996147917595</v>
+        <v>0.00324499614791759</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="F10" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="F11" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="G11" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>371.0795063055897</v>
+        <v>0.003710795063055898</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="F12" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="G12" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>412.4318125460267</v>
+        <v>0.004124318125460252</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="F13" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>422.1374183841095</v>
+        <v>0.004221374183841089</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="F14" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="F15" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>547.4486277268401</v>
+        <v>0.005474486277268402</v>
       </c>
     </row>
   </sheetData>
@@ -1035,13 +1035,13 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>547.4486277268401</v>
+        <v>0.005474486277268402</v>
       </c>
       <c r="D2" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="E2" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="D3" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="E3" t="n">
-        <v>539.999999999998</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.00155884572681198</v>
       </c>
     </row>
     <row r="4">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="D4" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="E4" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>155.8845726812011</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="D5" t="n">
-        <v>90.00000000000179</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="E5" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>155.8845726812011</v>
+        <v>0.001558845726811987</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.676380634307861e-08</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.705522537231445e-08</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>6.705522537231445e-08</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>4.656612873077393e-09</v>
+        <v>1.27897692436818e-13</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-8.381903171539307e-09</v>
+        <v>5.684341886080801e-14</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>30.00000000000013</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>8400000.000000037</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I2" t="n">
-        <v>2100000000.000009</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>155.8845726811993</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="G3" t="n">
-        <v>30.00000000000006</v>
+        <v>0.0003</v>
       </c>
       <c r="H3" t="n">
-        <v>8400000.000000019</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2100000000.000005</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>0.0009000000000000005</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>8400000</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="I4" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>155.884572681199</v>
+        <v>0.001558845726811989</v>
       </c>
       <c r="G5" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>8400000.000000004</v>
+        <v>83.99999999999994</v>
       </c>
       <c r="I5" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>180</v>
+        <v>0.0018</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>8400000</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>180.0000000000004</v>
+        <v>0.0018</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00000000000007</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>8400000.000000019</v>
+        <v>83.99999999999997</v>
       </c>
       <c r="I7" t="n">
-        <v>2100000000.000005</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001800000000000003</v>
       </c>
       <c r="G8" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003000000000000005</v>
       </c>
       <c r="H8" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="I8" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000004</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>155.884572681199</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="G9" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0002999999999999995</v>
       </c>
       <c r="H9" t="n">
-        <v>8400000.000000004</v>
+        <v>83.99999999999986</v>
       </c>
       <c r="I9" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999996</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>90.00000000000006</v>
+        <v>0.0008999999999999987</v>
       </c>
       <c r="G10" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0002999999999999995</v>
       </c>
       <c r="H10" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999987</v>
       </c>
       <c r="I10" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999997</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>180.0000000000004</v>
+        <v>0.001799999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>30.00000000000007</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>8400000.000000019</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>2100000000.000005</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>155.8845726811988</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="G12" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003</v>
       </c>
       <c r="H12" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="I12" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="G13" t="n">
-        <v>29.99999999999982</v>
+        <v>0.0003</v>
       </c>
       <c r="H13" t="n">
-        <v>8399999.99999995</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2099999999.999987</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>155.8845726811988</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="G14" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0002999999999999994</v>
       </c>
       <c r="H14" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999984</v>
       </c>
       <c r="I14" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999996</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>89.99999999999997</v>
+        <v>0.0009000000000000002</v>
       </c>
       <c r="G15" t="n">
-        <v>29.99999999999999</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>155.884572681199</v>
+        <v>0.001558845726811988</v>
       </c>
       <c r="G16" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>8400000.000000004</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I16" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>179.9999999999997</v>
+        <v>0.0018</v>
       </c>
       <c r="G17" t="n">
-        <v>29.99999999999995</v>
+        <v>0.0003</v>
       </c>
       <c r="H17" t="n">
-        <v>8399999.999999987</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
-        <v>2099999999.999997</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>179.9999999999995</v>
+        <v>0.001800000000000003</v>
       </c>
       <c r="G18" t="n">
-        <v>29.99999999999991</v>
+        <v>0.0003000000000000005</v>
       </c>
       <c r="H18" t="n">
-        <v>8399999.999999976</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="I18" t="n">
-        <v>2099999999.999994</v>
+        <v>21000.00000000004</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>180</v>
+        <v>0.0018</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0.0003</v>
       </c>
       <c r="H19" t="n">
-        <v>8400000</v>
+        <v>84</v>
       </c>
       <c r="I19" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>155.8845726811991</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="G20" t="n">
-        <v>30.00000000000003</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I20" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>89.99999999999994</v>
+        <v>0.0009000000000000002</v>
       </c>
       <c r="G21" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>8399999.999999994</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>179.9999999999995</v>
+        <v>0.001800000000000003</v>
       </c>
       <c r="G22" t="n">
-        <v>29.99999999999993</v>
+        <v>0.0003000000000000004</v>
       </c>
       <c r="H22" t="n">
-        <v>8399999.999999978</v>
+        <v>84.00000000000011</v>
       </c>
       <c r="I22" t="n">
-        <v>2099999999.999994</v>
+        <v>21000.00000000003</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>155.8845726811991</v>
+        <v>0.001558845726811988</v>
       </c>
       <c r="G23" t="n">
-        <v>30.00000000000003</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>8400000.000000009</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I23" t="n">
-        <v>2100000000.000002</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0003000000000000003</v>
       </c>
       <c r="H24" t="n">
-        <v>8400000.000000006</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="I24" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000002</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>89.99999999999991</v>
+        <v>0.0009000000000000006</v>
       </c>
       <c r="G25" t="n">
-        <v>29.99999999999997</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>8399999.999999991</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="I25" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>90.00000000000003</v>
+        <v>0.0009</v>
       </c>
       <c r="G26" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0003</v>
       </c>
       <c r="H26" t="n">
-        <v>8400000.000000002</v>
+        <v>84</v>
       </c>
       <c r="I26" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="27">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>89.99999999999993</v>
+        <v>0.0009000000000000004</v>
       </c>
       <c r="G27" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I27" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2081,16 +2081,16 @@
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>0.0008999999999999997</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>8400000</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="I28" t="n">
-        <v>2100000000</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2112,16 +2112,16 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>89.99999999999989</v>
+        <v>0.0009000000000000005</v>
       </c>
       <c r="G29" t="n">
-        <v>29.99999999999996</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H29" t="n">
-        <v>8399999.999999989</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="I29" t="n">
-        <v>2099999999.999997</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2143,16 +2143,16 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>89.99999999999993</v>
+        <v>0.0009000000000000003</v>
       </c>
       <c r="G30" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I30" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
       <c r="G31" t="n">
-        <v>30.00000000000005</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>8400000.000000013</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2100000000.000003</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001799999999999998</v>
       </c>
       <c r="G32" t="n">
-        <v>29.99999999999999</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H32" t="n">
-        <v>8399999.999999996</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I32" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>201.2461179749812</v>
+        <v>0.002012461179749812</v>
       </c>
       <c r="G33" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H33" t="n">
-        <v>8400000.000000004</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="I33" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>201.2461179749808</v>
+        <v>0.00201246117974981</v>
       </c>
       <c r="G34" t="n">
-        <v>29.99999999999995</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>8399999.999999987</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>2099999999.999997</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>180.0000000000002</v>
+        <v>0.0018</v>
       </c>
       <c r="G35" t="n">
-        <v>30.00000000000003</v>
+        <v>0.0003</v>
       </c>
       <c r="H35" t="n">
-        <v>8400000.000000007</v>
+        <v>84</v>
       </c>
       <c r="I35" t="n">
-        <v>2100000000.000002</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001799999999999998</v>
       </c>
       <c r="G36" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0002999999999999996</v>
       </c>
       <c r="H36" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999989</v>
       </c>
       <c r="I36" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999997</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>201.2461179749812</v>
+        <v>0.002012461179749812</v>
       </c>
       <c r="G37" t="n">
-        <v>30.00000000000001</v>
+        <v>0.0003000000000000002</v>
       </c>
       <c r="H37" t="n">
-        <v>8400000.000000004</v>
+        <v>84.00000000000007</v>
       </c>
       <c r="I37" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000002</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>201.2461179749809</v>
+        <v>0.002012461179749811</v>
       </c>
       <c r="G38" t="n">
-        <v>29.99999999999997</v>
+        <v>0.0003</v>
       </c>
       <c r="H38" t="n">
-        <v>8399999.999999993</v>
+        <v>84</v>
       </c>
       <c r="I38" t="n">
-        <v>2099999999.999998</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>180.0000000000002</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>30.00000000000004</v>
+        <v>0.0003000000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="I39" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001799999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0002999999999999998</v>
       </c>
       <c r="H40" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="I40" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999998</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>201.2461179749813</v>
+        <v>0.002012461179749813</v>
       </c>
       <c r="G41" t="n">
-        <v>30.00000000000003</v>
+        <v>0.0003000000000000003</v>
       </c>
       <c r="H41" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="I41" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000002</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>201.2461179749808</v>
+        <v>0.00201246117974981</v>
       </c>
       <c r="G42" t="n">
-        <v>29.99999999999996</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>8399999.999999989</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>2099999999.999997</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>180.0000000000001</v>
+        <v>0.001799999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>30.00000000000002</v>
+        <v>0.0002999999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="I43" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999999</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>179.9999999999999</v>
+        <v>0.0018</v>
       </c>
       <c r="G44" t="n">
-        <v>29.99999999999998</v>
+        <v>0.0003</v>
       </c>
       <c r="H44" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="I44" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>8400000.000000037</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F2" t="n">
-        <v>2100000000.000009</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="N2" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2.329516727335206e-12</v>
+        <v>-3.29262008803703e-18</v>
       </c>
       <c r="AA2" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3.91155481338501e-08</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.91155481338501e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>8400000.000000019</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2100000000.000005</v>
+        <v>21000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="N3" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="O3" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>155.8845726811993</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.179500941361766e-12</v>
+        <v>2.818925648462312e-18</v>
       </c>
       <c r="AA3" t="n">
-        <v>-8.093987077986736e-13</v>
+        <v>-4.753737175074203e-18</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>8400000</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="F4" t="n">
-        <v>2100000000</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H4" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.165290086646564e-12</v>
+        <v>2.710505431213761e-18</v>
       </c>
       <c r="T4" t="n">
-        <v>155.8845726811993</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="U4" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>90.00000000000117</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="Z4" t="n">
-        <v>155.8845726811992</v>
+        <v>0.001558845726811989</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>8400000.000000004</v>
+        <v>83.99999999999994</v>
       </c>
       <c r="F5" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H5" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I5" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="N5" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>155.8845726811993</v>
+        <v>0.00155884572681199</v>
       </c>
       <c r="T5" t="n">
-        <v>1.179500941361766e-12</v>
+        <v>2.818925648462312e-18</v>
       </c>
       <c r="U5" t="n">
-        <v>-8.093987077986736e-13</v>
+        <v>-4.753737175074203e-18</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>311.7691453623983</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>2.818925648462312e-18</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.862315955609786e-12</v>
+        <v>-1.273119217156146e-17</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-9.947598300641403e-14</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>8400000</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
       <c r="G6" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H6" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="N6" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>89.99999999999963</v>
+        <v>0.0008999999999999976</v>
       </c>
       <c r="T6" t="n">
-        <v>155.8845726812001</v>
+        <v>0.001558845726811992</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.329516727335206e-12</v>
+        <v>-3.29262008803703e-18</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>269.9999999999997</v>
+        <v>0.002699999999999998</v>
       </c>
       <c r="Z6" t="n">
-        <v>155.8845726812004</v>
+        <v>0.001558845726811991</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.862315955609786e-12</v>
+        <v>-1.273119217156146e-17</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>8400000.000000019</v>
+        <v>83.99999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>2100000000.000005</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H7" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="N7" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.329516727335206e-12</v>
+        <v>-3.29262008803703e-18</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="Z7" t="n">
-        <v>-7.292197765110538e-12</v>
+        <v>-3.519396974980317e-18</v>
       </c>
       <c r="AA7" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-2.048909664154053e-08</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.048909664154053e-08</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="F8" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000004</v>
       </c>
       <c r="G8" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H8" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="N8" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="O8" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.392663762089796e-12</v>
+        <v>2.602085213965211e-18</v>
       </c>
       <c r="T8" t="n">
-        <v>311.7691453623984</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="U8" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>180.0000000000013</v>
+        <v>0.001800000000000006</v>
       </c>
       <c r="Z8" t="n">
-        <v>311.7691453623985</v>
+        <v>0.003117691453623977</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-1.4210854715202e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>8400000.000000004</v>
+        <v>83.99999999999986</v>
       </c>
       <c r="F9" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999996</v>
       </c>
       <c r="G9" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H9" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="N9" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="O9" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>155.8845726812004</v>
+        <v>0.001558845726811991</v>
       </c>
       <c r="T9" t="n">
-        <v>269.9999999999997</v>
+        <v>0.002699999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>311.7691453623994</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="Z9" t="n">
-        <v>270</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>1.84741111297626e-13</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-1.84741111297626e-13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999987</v>
       </c>
       <c r="F10" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999997</v>
       </c>
       <c r="G10" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H10" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="N10" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="O10" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001799999999999995</v>
       </c>
       <c r="T10" t="n">
-        <v>311.7691453623993</v>
+        <v>0.003117691453623983</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.292197765110538e-12</v>
+        <v>-3.519396974980317e-18</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>270</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="Z10" t="n">
-        <v>311.7691453623995</v>
+        <v>0.003117691453623979</v>
       </c>
       <c r="AA10" t="n">
-        <v>-8.25034530002525e-12</v>
+        <v>-6.620434362867334e-18</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-1.4210854715202e-13</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>8400000.000000019</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="F11" t="n">
-        <v>2100000000.000005</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H11" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N11" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.292197765110538e-12</v>
+        <v>-3.519396974980317e-18</v>
       </c>
       <c r="U11" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.421950808161317e-11</v>
+        <v>3.910240474061865e-18</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G12" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="H12" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="I12" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N12" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>311.7691453623994</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="T12" t="n">
-        <v>270</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="U12" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>467.6537180435982</v>
+        <v>0.004676537180435968</v>
       </c>
       <c r="Z12" t="n">
-        <v>270.0000000000008</v>
+        <v>0.0027</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>8399999.99999995</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2099999999.999987</v>
+        <v>21000</v>
       </c>
       <c r="G13" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N13" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="O13" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-90.00000000000006</v>
+        <v>-0.000900000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="Z13" t="n">
-        <v>-90.00000000000236</v>
+        <v>-0.0009000000000000032</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999984</v>
       </c>
       <c r="F14" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999996</v>
       </c>
       <c r="G14" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="N14" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-90.00000000000006</v>
+        <v>-0.000900000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>155.8845726811988</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="Z14" t="n">
-        <v>-2.586375558166765e-12</v>
+        <v>7.155734338404329e-18</v>
       </c>
       <c r="AA14" t="n">
-        <v>-90.00000000000072</v>
+        <v>-0.0009000000000000054</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>5.587935447692871e-09</v>
+        <v>1.84741111297626e-13</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-5.587935447692871e-09</v>
+        <v>-1.84741111297626e-13</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>8399999.999999996</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G15" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="H15" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N15" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="O15" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.600586412881967e-12</v>
+        <v>7.047314121155779e-18</v>
       </c>
       <c r="T15" t="n">
-        <v>155.8845726811988</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="U15" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>89.99999999999737</v>
+        <v>0.0009000000000000072</v>
       </c>
       <c r="Z15" t="n">
-        <v>155.8845726811992</v>
+        <v>0.001558845726811985</v>
       </c>
       <c r="AA15" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>8400000.000000004</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F16" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G16" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="H16" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N16" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>155.8845726811988</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.586375558166765e-12</v>
+        <v>7.155734338404329e-18</v>
       </c>
       <c r="U16" t="n">
-        <v>-90.00000000000072</v>
+        <v>-0.0009000000000000054</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>311.7691453623979</v>
+        <v>0.003117691453623975</v>
       </c>
       <c r="Z16" t="n">
-        <v>-2.472688720445149e-12</v>
+        <v>8.456776945386935e-18</v>
       </c>
       <c r="AA16" t="n">
-        <v>-90.00000000000179</v>
+        <v>-0.0009000000000000131</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-9.947598300641403e-14</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>8399999.999999987</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>2099999999.999997</v>
+        <v>21000</v>
       </c>
       <c r="G17" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="H17" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="I17" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N17" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>90.00000000000155</v>
+        <v>0.0008999999999999925</v>
       </c>
       <c r="T17" t="n">
-        <v>155.8845726811968</v>
+        <v>0.001558845726811994</v>
       </c>
       <c r="U17" t="n">
-        <v>-90.00000000000236</v>
+        <v>-0.0009000000000000032</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002699999999999992</v>
       </c>
       <c r="Z17" t="n">
-        <v>155.8845726811968</v>
+        <v>0.001558845726811995</v>
       </c>
       <c r="AA17" t="n">
-        <v>-90.00000000000179</v>
+        <v>-0.0009000000000000131</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>8399999.999999976</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="F18" t="n">
-        <v>2099999999.999994</v>
+        <v>21000.00000000004</v>
       </c>
       <c r="G18" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="H18" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="I18" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N18" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O18" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="T18" t="n">
-        <v>-90.00000000000236</v>
+        <v>-0.0009000000000000032</v>
       </c>
       <c r="U18" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="Z18" t="n">
-        <v>-90.00000000000729</v>
+        <v>-0.0009000000000000031</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>-1.27897692436818e-13</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>1.27897692436818e-13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>8400000</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
       <c r="G19" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="H19" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N19" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O19" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.472688720445149e-12</v>
+        <v>8.239936510889834e-18</v>
       </c>
       <c r="T19" t="n">
-        <v>311.7691453623979</v>
+        <v>0.003117691453623975</v>
       </c>
       <c r="U19" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>179.9999999999976</v>
+        <v>0.001800000000000008</v>
       </c>
       <c r="Z19" t="n">
-        <v>311.7691453623975</v>
+        <v>0.003117691453623978</v>
       </c>
       <c r="AA19" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F20" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="H20" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N20" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O20" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>155.8845726811968</v>
+        <v>0.001558845726811995</v>
       </c>
       <c r="T20" t="n">
-        <v>270.0000000000013</v>
+        <v>0.002699999999999992</v>
       </c>
       <c r="U20" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>311.7691453623959</v>
+        <v>0.003117691453623985</v>
       </c>
       <c r="Z20" t="n">
-        <v>270.0000000000008</v>
+        <v>0.002699999999999995</v>
       </c>
       <c r="AA20" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>8399999.999999994</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G21" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="H21" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="I21" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N21" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O21" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>180.0000000000009</v>
+        <v>0.001799999999999995</v>
       </c>
       <c r="T21" t="n">
-        <v>311.7691453623956</v>
+        <v>0.003117691453623986</v>
       </c>
       <c r="U21" t="n">
-        <v>-90.00000000000729</v>
+        <v>-0.0009000000000000031</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>270.0000000000008</v>
+        <v>0.002699999999999995</v>
       </c>
       <c r="Z21" t="n">
-        <v>311.7691453623959</v>
+        <v>0.003117691453623985</v>
       </c>
       <c r="AA21" t="n">
-        <v>-90.00000000000814</v>
+        <v>-0.0009000000000000071</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>8399999.999999978</v>
+        <v>84.00000000000011</v>
       </c>
       <c r="F22" t="n">
-        <v>2099999999.999994</v>
+        <v>21000.00000000003</v>
       </c>
       <c r="G22" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="H22" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="I22" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N22" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="T22" t="n">
-        <v>-90.00000000000729</v>
+        <v>-0.0009000000000000031</v>
       </c>
       <c r="U22" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="Z22" t="n">
-        <v>-90.00000000001415</v>
+        <v>-0.0008999999999999964</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>8400000.000000009</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F23" t="n">
-        <v>2100000000.000002</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G23" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="H23" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="I23" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N23" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>311.7691453623959</v>
+        <v>0.003117691453623985</v>
       </c>
       <c r="T23" t="n">
-        <v>270.0000000000008</v>
+        <v>0.002699999999999995</v>
       </c>
       <c r="U23" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>467.6537180435951</v>
+        <v>0.004676537180435973</v>
       </c>
       <c r="Z23" t="n">
-        <v>269.999999999999</v>
+        <v>0.002700000000000003</v>
       </c>
       <c r="AA23" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>8400000.000000006</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="F24" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000002</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>8399999.999999991</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="F25" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H25" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I25" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="N25" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="T25" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="Z25" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>8400000.000000002</v>
+        <v>84</v>
       </c>
       <c r="F26" t="n">
-        <v>2100000000</v>
+        <v>21000</v>
       </c>
       <c r="G26" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H26" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N26" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="O26" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="T26" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="Z26" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F27" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H27" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N27" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="T27" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="Z27" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6157,19 +6157,19 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>8400000</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="F28" t="n">
-        <v>2100000000</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H28" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="I28" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N28" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O28" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="T28" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="U28" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="Z28" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -6285,19 +6285,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>8399999.999999989</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="F29" t="n">
-        <v>2099999999.999997</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="H29" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="I29" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N29" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O29" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="T29" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="U29" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="Z29" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="AA29" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6413,16 +6413,16 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>8399999.999999993</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F30" t="n">
-        <v>2099999999.999998</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="H30" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N30" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="T30" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="Z30" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>5.587935447692871e-09</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>-5.587935447692871e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>8400000.000000013</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>2100000000.000003</v>
+        <v>21000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="N31" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>180.0000000000003</v>
+        <v>0.0018</v>
       </c>
       <c r="Z31" t="n">
-        <v>-2.401634446869139e-12</v>
+        <v>1.409462824231156e-18</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.172395514004165e-12</v>
+        <v>-9.324138683375338e-18</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>8399999.999999996</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F32" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G32" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="N32" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="O32" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-45.00000000000003</v>
+        <v>-0.0004500000000000005</v>
       </c>
       <c r="T32" t="n">
-        <v>51.02520385624571</v>
+        <v>0.0005102520385624573</v>
       </c>
       <c r="U32" t="n">
-        <v>-58.91883036371799</v>
+        <v>-0.0005891883036371801</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>134.9999999999999</v>
+        <v>0.001349999999999998</v>
       </c>
       <c r="Z32" t="n">
-        <v>51.02520385624714</v>
+        <v>0.0005102520385624617</v>
       </c>
       <c r="AA32" t="n">
-        <v>-58.91883036371783</v>
+        <v>-0.0005891883036371809</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>8400000.000000004</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="F33" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="N33" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="O33" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>201.2461179749812</v>
+        <v>0.002012461179749812</v>
       </c>
       <c r="Z33" t="n">
-        <v>-2.586375558166765e-12</v>
+        <v>-3.035766082959412e-18</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>8399999.999999987</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>2099999999.999997</v>
+        <v>21000</v>
       </c>
       <c r="G34" t="n">
-        <v>90.00000000000006</v>
+        <v>0.000900000000000001</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="N34" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>-40.24922359499624</v>
+        <v>-0.0004024922359499625</v>
       </c>
       <c r="T34" t="n">
-        <v>80.49844718999248</v>
+        <v>0.0008049844718999251</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>160.9968943799845</v>
+        <v>0.001609968943799848</v>
       </c>
       <c r="Z34" t="n">
-        <v>80.49844718999488</v>
+        <v>0.0008049844718999276</v>
       </c>
       <c r="AA34" t="n">
-        <v>8.898460371464397e-13</v>
+        <v>3.21025446370383e-18</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>8400000.000000007</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
-        <v>2100000000.000002</v>
+        <v>21000</v>
       </c>
       <c r="G35" t="n">
-        <v>8.093987077986736e-13</v>
+        <v>4.753737175074203e-18</v>
       </c>
       <c r="H35" t="n">
-        <v>135.0000000000009</v>
+        <v>0.001350000000000002</v>
       </c>
       <c r="I35" t="n">
-        <v>77.94228634059863</v>
+        <v>0.0007794228634059925</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="N35" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>135.0000000000007</v>
+        <v>0.001350000000000003</v>
       </c>
       <c r="T35" t="n">
-        <v>51.02520385624623</v>
+        <v>0.0005102520385624563</v>
       </c>
       <c r="U35" t="n">
-        <v>58.91883036371676</v>
+        <v>0.0005891883036371746</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>315.0000000000009</v>
+        <v>0.003150000000000003</v>
       </c>
       <c r="Z35" t="n">
-        <v>51.0252038562428</v>
+        <v>0.0005102520385624543</v>
       </c>
       <c r="AA35" t="n">
-        <v>58.91883036371838</v>
+        <v>0.0005891883036371637</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-9.313225746154785e-09</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>9.313225746154785e-09</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999989</v>
       </c>
       <c r="F36" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999997</v>
       </c>
       <c r="G36" t="n">
-        <v>90.00000000000072</v>
+        <v>0.0009000000000000054</v>
       </c>
       <c r="H36" t="n">
-        <v>134.9999999999986</v>
+        <v>0.001350000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>77.94228634060167</v>
+        <v>0.0007794228634059872</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="N36" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>89.99999999999955</v>
+        <v>0.0008999999999999949</v>
       </c>
       <c r="T36" t="n">
-        <v>102.0504077124898</v>
+        <v>0.001020504077124921</v>
       </c>
       <c r="U36" t="n">
-        <v>-117.837660727438</v>
+        <v>-0.001178376607274357</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>269.9999999999994</v>
+        <v>0.002699999999999993</v>
       </c>
       <c r="Z36" t="n">
-        <v>102.0504077124936</v>
+        <v>0.001020504077124923</v>
       </c>
       <c r="AA36" t="n">
-        <v>-117.8376607274363</v>
+        <v>-0.001178376607274365</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>9.947598300641403e-14</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>-9.947598300641403e-14</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>8400000.000000004</v>
+        <v>84.00000000000007</v>
       </c>
       <c r="F37" t="n">
-        <v>2100000000.000001</v>
+        <v>21000.00000000002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.329516727335206e-12</v>
+        <v>3.29262008803703e-18</v>
       </c>
       <c r="H37" t="n">
-        <v>180.0000000000008</v>
+        <v>0.001800000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="N37" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="O37" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>160.9968943799866</v>
+        <v>0.001609968943799851</v>
       </c>
       <c r="T37" t="n">
-        <v>80.4984471899907</v>
+        <v>0.0008049844718999217</v>
       </c>
       <c r="U37" t="n">
-        <v>-8.898460371464397e-13</v>
+        <v>-3.21025446370383e-18</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>362.2430123549678</v>
+        <v>0.003622430123549663</v>
       </c>
       <c r="Z37" t="n">
-        <v>80.49844718998521</v>
+        <v>0.0008049844718999229</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>8399999.999999993</v>
+        <v>84</v>
       </c>
       <c r="F38" t="n">
-        <v>2099999999.999998</v>
+        <v>21000</v>
       </c>
       <c r="G38" t="n">
-        <v>90.00000000000236</v>
+        <v>0.0009000000000000032</v>
       </c>
       <c r="H38" t="n">
-        <v>179.9999999999989</v>
+        <v>0.0018</v>
       </c>
       <c r="I38" t="n">
-        <v>2.411826243744093e-12</v>
+        <v>-8.564521398736833e-18</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="N38" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="O38" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>120.7476707849866</v>
+        <v>0.001207476707849885</v>
       </c>
       <c r="T38" t="n">
-        <v>160.9968943799865</v>
+        <v>0.001609968943799851</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.411826243744093e-12</v>
+        <v>8.564521398736833e-18</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>321.9937887599675</v>
+        <v>0.003219937887599696</v>
       </c>
       <c r="Z38" t="n">
-        <v>160.9968943799919</v>
+        <v>0.001609968943799852</v>
       </c>
       <c r="AA38" t="n">
-        <v>7.420198735505002e-13</v>
+        <v>6.421903002751408e-18</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F39" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>1.862315955609786e-12</v>
+        <v>1.273119217156146e-17</v>
       </c>
       <c r="H39" t="n">
-        <v>270.0000000000011</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>155.884572681198</v>
+        <v>0.001558845726811987</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="N39" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="O39" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>135.0000000000022</v>
+        <v>0.001350000000000008</v>
       </c>
       <c r="T39" t="n">
-        <v>255.1260192812276</v>
+        <v>0.002551260192812276</v>
       </c>
       <c r="U39" t="n">
-        <v>117.8376607274363</v>
+        <v>0.001178376607274365</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>315.0000000000024</v>
+        <v>0.003150000000000009</v>
       </c>
       <c r="Z39" t="n">
-        <v>255.1260192812237</v>
+        <v>0.002551260192812278</v>
       </c>
       <c r="AA39" t="n">
-        <v>117.8376607274425</v>
+        <v>0.001178376607274358</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-1.30385160446167e-08</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.30385160446167e-08</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>8399999.999999994</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="F40" t="n">
-        <v>2099999999.999999</v>
+        <v>20999.99999999998</v>
       </c>
       <c r="G40" t="n">
-        <v>90.00000000000179</v>
+        <v>0.0009000000000000131</v>
       </c>
       <c r="H40" t="n">
-        <v>269.9999999999987</v>
+        <v>0.002700000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>155.8845726812011</v>
+        <v>0.00155884572681198</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="N40" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="O40" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>89.99999999999726</v>
+        <v>0.0008999999999999977</v>
       </c>
       <c r="T40" t="n">
-        <v>306.1512231374753</v>
+        <v>0.003061512231374744</v>
       </c>
       <c r="U40" t="n">
-        <v>-58.91883036371838</v>
+        <v>-0.0005891883036371637</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>269.9999999999972</v>
+        <v>0.002699999999999996</v>
       </c>
       <c r="Z40" t="n">
-        <v>306.1512231374792</v>
+        <v>0.003061512231374739</v>
       </c>
       <c r="AA40" t="n">
-        <v>-58.91883036371196</v>
+        <v>-0.0005891883036371709</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>7.105427357601002e-14</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-1.862645149230957e-09</v>
+        <v>-7.105427357601002e-14</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>8400000.000000009</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="F41" t="n">
-        <v>2100000000.000002</v>
+        <v>21000.00000000002</v>
       </c>
       <c r="G41" t="n">
-        <v>7.292197765110538e-12</v>
+        <v>3.519396974980317e-18</v>
       </c>
       <c r="H41" t="n">
-        <v>360.0000000000012</v>
+        <v>0.0036</v>
       </c>
       <c r="I41" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N41" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>321.993788759974</v>
+        <v>0.003219937887599699</v>
       </c>
       <c r="T41" t="n">
-        <v>160.9968943799789</v>
+        <v>0.001609968943799845</v>
       </c>
       <c r="U41" t="n">
-        <v>-7.420198735505002e-13</v>
+        <v>-6.421903002751408e-18</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>523.2399067349553</v>
+        <v>0.005232399067349512</v>
       </c>
       <c r="Z41" t="n">
-        <v>160.9968943799713</v>
+        <v>0.001609968943799854</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-9.313225746154785e-09</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>9.313225746154785e-09</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>8399999.999999989</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>2099999999.999997</v>
+        <v>21000</v>
       </c>
       <c r="G42" t="n">
-        <v>90.00000000000729</v>
+        <v>0.0009000000000000031</v>
       </c>
       <c r="H42" t="n">
-        <v>359.9999999999984</v>
+        <v>0.003600000000000003</v>
       </c>
       <c r="I42" t="n">
-        <v>1.909017094802782e-12</v>
+        <v>-7.708358245815531e-18</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N42" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>281.7445651649688</v>
+        <v>0.002817445651649736</v>
       </c>
       <c r="T42" t="n">
-        <v>241.4953415699831</v>
+        <v>0.002414953415699777</v>
       </c>
       <c r="U42" t="n">
-        <v>-1.909017094802782e-12</v>
+        <v>7.708358245815531e-18</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>482.9906831399496</v>
+        <v>0.004829906831399547</v>
       </c>
       <c r="Z42" t="n">
-        <v>241.4953415699907</v>
+        <v>0.002414953415699769</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.30385160446167e-08</v>
+        <v>7.105427357601002e-14</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-1.30385160446167e-08</v>
+        <v>-7.105427357601002e-14</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>8400000.000000006</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="F43" t="n">
-        <v>2100000000.000001</v>
+        <v>20999.99999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>8.25034530002525e-12</v>
+        <v>6.620434362867334e-18</v>
       </c>
       <c r="H43" t="n">
-        <v>405.0000000000013</v>
+        <v>0.004049999999999996</v>
       </c>
       <c r="I43" t="n">
-        <v>77.94228634059871</v>
+        <v>0.0007794228634059893</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>90.00000000001415</v>
+        <v>0.0008999999999999964</v>
       </c>
       <c r="N43" t="n">
-        <v>539.999999999998</v>
+        <v>0.005400000000000005</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>270.0000000000055</v>
+        <v>0.002700000000000003</v>
       </c>
       <c r="T43" t="n">
-        <v>306.1512231374699</v>
+        <v>0.003061512231374732</v>
       </c>
       <c r="U43" t="n">
-        <v>58.91883036372276</v>
+        <v>0.0005891883036371796</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>450.0000000000056</v>
+        <v>0.004500000000000002</v>
       </c>
       <c r="Z43" t="n">
-        <v>306.1512231374647</v>
+        <v>0.003061512231374746</v>
       </c>
       <c r="AA43" t="n">
-        <v>58.91883036372722</v>
+        <v>0.0005891883036371771</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>8399999.999999994</v>
+        <v>84</v>
       </c>
       <c r="F44" t="n">
-        <v>2099999999.999999</v>
+        <v>21000</v>
       </c>
       <c r="G44" t="n">
-        <v>90.00000000000814</v>
+        <v>0.0009000000000000071</v>
       </c>
       <c r="H44" t="n">
-        <v>404.9999999999987</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="I44" t="n">
-        <v>77.94228634060116</v>
+        <v>0.0007794228634059876</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.421950808161317e-11</v>
+        <v>-3.910240474061865e-18</v>
       </c>
       <c r="N44" t="n">
-        <v>540.0000000000016</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>224.9999999999942</v>
+        <v>0.002250000000000002</v>
       </c>
       <c r="T44" t="n">
-        <v>357.1764269937244</v>
+        <v>0.0035717642699372</v>
       </c>
       <c r="U44" t="n">
-        <v>4.071409875905374e-12</v>
+        <v>1.008308020411519e-17</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>404.9999999999941</v>
+        <v>0.004050000000000002</v>
       </c>
       <c r="Z44" t="n">
-        <v>357.1764269937289</v>
+        <v>0.003571764269937195</v>
       </c>
       <c r="AA44" t="n">
-        <v>9.30885316128981e-12</v>
+        <v>-2.559853279695501e-18</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_temperature.xlsx
+++ b/outputs/validation_truss_temperature.xlsx
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-84.00000000000003</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-84.00000000000001</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>-84.00000000000004</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>9.947598300641403e-14</v>
+        <v>-83.99999999999994</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-9.947598300641403e-14</v>
+        <v>83.99999999999994</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>-84.00000000000001</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>-83.99999999999997</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>83.99999999999997</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-1.4210854715202e-13</v>
+        <v>-84.00000000000014</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.84741111297626e-13</v>
+        <v>-83.99999999999986</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.84741111297626e-13</v>
+        <v>83.99999999999986</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>-83.99999999999987</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.4210854715202e-13</v>
+        <v>83.99999999999987</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>-83.99999999999996</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>-84</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-83.99999999999999</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.84741111297626e-13</v>
+        <v>-83.99999999999984</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-1.84741111297626e-13</v>
+        <v>83.99999999999984</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>-84.00000000000001</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>9.947598300641403e-14</v>
+        <v>-83.99999999999993</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-9.947598300641403e-14</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-84</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>84</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-1.27897692436818e-13</v>
+        <v>-84.00000000000014</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.27897692436818e-13</v>
+        <v>84.00000000000014</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-84</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>84</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>-84.00000000000003</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-84.00000000000001</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-84.00000000000011</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>84.00000000000011</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>-83.99999999999993</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>-84.00000000000009</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-84.00000000000006</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-84</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>84</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-84.00000000000003</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>-83.99999999999996</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>-84.00000000000004</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>84.00000000000004</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-84.00000000000003</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>-84.00000000000001</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>-83.99999999999993</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>-84.00000000000006</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>84.00000000000006</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>-83.99999999999999</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-84</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>9.947598300641403e-14</v>
+        <v>-83.99999999999989</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-9.947598300641403e-14</v>
+        <v>83.99999999999989</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>-84.00000000000007</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>84.00000000000007</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>-84</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>84</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>-84.00000000000003</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>7.105427357601002e-14</v>
+        <v>-83.99999999999993</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-7.105427357601002e-14</v>
+        <v>83.99999999999993</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-84.00000000000009</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>84.00000000000009</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>7.105427357601002e-14</v>
+        <v>-83.99999999999999</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-7.105427357601002e-14</v>
+        <v>83.99999999999999</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>-83.99999999999996</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>83.99999999999996</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-84</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>84</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
